--- a/Supplementary_Data_4_shortlisted_candidate_compounds.xlsx
+++ b/Supplementary_Data_4_shortlisted_candidate_compounds.xlsx
@@ -1,17 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
   <workbookPr/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{39E93DB3-CB20-4545-821B-EB67C8BFC6D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="1189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="1188">
   <si>
     <t>inchikey</t>
   </si>
@@ -1489,7 +1509,7 @@
     <t>RYMZZMVNJRMUDD-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>Simvastatin</t>
+    <t>candidate1</t>
   </si>
   <si>
     <t>BRD-A81772229</t>
@@ -2411,9 +2431,6 @@
   </si>
   <si>
     <t>RYMZZMVNJRMUDD-HGQWONQESA-N</t>
-  </si>
-  <si>
-    <t>simvastatin</t>
   </si>
   <si>
     <t>BRD-K22134346</t>
@@ -3583,25 +3600,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="8.0"/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -3611,7 +3629,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -3633,66 +3651,54 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -3882,22 +3888,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C1000"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="35.38"/>
-    <col customWidth="1" min="2" max="2" width="24.5"/>
-    <col customWidth="1" min="3" max="3" width="15.13"/>
+    <col min="1" max="1" width="35.42578125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3908,7 +3917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -3919,7 +3928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -3930,7 +3939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -3941,7 +3950,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
@@ -3952,7 +3961,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -3963,7 +3972,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
@@ -3974,7 +3983,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -3985,7 +3994,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -3996,7 +4005,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3">
       <c r="A10" s="3" t="s">
         <v>22</v>
       </c>
@@ -4007,7 +4016,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -4018,7 +4027,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
@@ -4029,7 +4038,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
@@ -4040,7 +4049,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3">
       <c r="A14" s="3" t="s">
         <v>32</v>
       </c>
@@ -4051,7 +4060,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
         <v>35</v>
       </c>
@@ -4062,7 +4071,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
         <v>38</v>
       </c>
@@ -4073,7 +4082,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
         <v>40</v>
       </c>
@@ -4084,7 +4093,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3">
       <c r="A18" s="3" t="s">
         <v>42</v>
       </c>
@@ -4095,7 +4104,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
         <v>44</v>
       </c>
@@ -4106,7 +4115,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3">
       <c r="A20" s="3" t="s">
         <v>47</v>
       </c>
@@ -4117,7 +4126,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
         <v>50</v>
       </c>
@@ -4128,7 +4137,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
         <v>53</v>
       </c>
@@ -4139,7 +4148,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
         <v>56</v>
       </c>
@@ -4150,7 +4159,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
         <v>58</v>
       </c>
@@ -4161,7 +4170,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
         <v>61</v>
       </c>
@@ -4172,7 +4181,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
         <v>64</v>
       </c>
@@ -4183,7 +4192,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
         <v>67</v>
       </c>
@@ -4194,7 +4203,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
         <v>70</v>
       </c>
@@ -4205,7 +4214,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
         <v>73</v>
       </c>
@@ -4216,7 +4225,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3">
       <c r="A30" s="3" t="s">
         <v>76</v>
       </c>
@@ -4227,7 +4236,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
         <v>78</v>
       </c>
@@ -4238,7 +4247,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3">
       <c r="A32" s="3" t="s">
         <v>80</v>
       </c>
@@ -4249,7 +4258,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
         <v>82</v>
       </c>
@@ -4260,7 +4269,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3">
       <c r="A34" s="3" t="s">
         <v>85</v>
       </c>
@@ -4271,7 +4280,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
         <v>87</v>
       </c>
@@ -4282,7 +4291,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3">
       <c r="A36" s="3" t="s">
         <v>90</v>
       </c>
@@ -4293,7 +4302,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
         <v>93</v>
       </c>
@@ -4304,7 +4313,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3">
       <c r="A38" s="3" t="s">
         <v>95</v>
       </c>
@@ -4315,7 +4324,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
         <v>98</v>
       </c>
@@ -4326,7 +4335,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3">
       <c r="A40" s="3" t="s">
         <v>101</v>
       </c>
@@ -4337,7 +4346,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
         <v>104</v>
       </c>
@@ -4348,7 +4357,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3">
       <c r="A42" s="3" t="s">
         <v>107</v>
       </c>
@@ -4359,7 +4368,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
         <v>110</v>
       </c>
@@ -4370,7 +4379,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3">
       <c r="A44" s="3" t="s">
         <v>113</v>
       </c>
@@ -4381,7 +4390,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
         <v>115</v>
       </c>
@@ -4392,7 +4401,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:3">
       <c r="A46" s="3" t="s">
         <v>118</v>
       </c>
@@ -4403,7 +4412,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
         <v>121</v>
       </c>
@@ -4414,7 +4423,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3">
       <c r="A48" s="3" t="s">
         <v>124</v>
       </c>
@@ -4425,7 +4434,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
         <v>127</v>
       </c>
@@ -4436,7 +4445,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:3">
       <c r="A50" s="3" t="s">
         <v>129</v>
       </c>
@@ -4447,7 +4456,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
         <v>131</v>
       </c>
@@ -4458,7 +4467,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:3">
       <c r="A52" s="3" t="s">
         <v>133</v>
       </c>
@@ -4469,7 +4478,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:3">
       <c r="A53" s="2" t="s">
         <v>135</v>
       </c>
@@ -4480,7 +4489,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:3">
       <c r="A54" s="3" t="s">
         <v>137</v>
       </c>
@@ -4491,7 +4500,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:3">
       <c r="A55" s="2" t="s">
         <v>140</v>
       </c>
@@ -4502,7 +4511,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:3">
       <c r="A56" s="3" t="s">
         <v>143</v>
       </c>
@@ -4513,7 +4522,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:3">
       <c r="A57" s="2" t="s">
         <v>146</v>
       </c>
@@ -4524,7 +4533,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:3">
       <c r="A58" s="3" t="s">
         <v>148</v>
       </c>
@@ -4535,7 +4544,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:3">
       <c r="A59" s="2" t="s">
         <v>151</v>
       </c>
@@ -4546,7 +4555,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:3">
       <c r="A60" s="3" t="s">
         <v>153</v>
       </c>
@@ -4557,7 +4566,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:3">
       <c r="A61" s="2" t="s">
         <v>156</v>
       </c>
@@ -4568,7 +4577,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:3">
       <c r="A62" s="3" t="s">
         <v>158</v>
       </c>
@@ -4579,7 +4588,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:3">
       <c r="A63" s="2" t="s">
         <v>160</v>
       </c>
@@ -4590,7 +4599,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:3">
       <c r="A64" s="3" t="s">
         <v>162</v>
       </c>
@@ -4601,7 +4610,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:3">
       <c r="A65" s="2" t="s">
         <v>164</v>
       </c>
@@ -4612,7 +4621,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:3">
       <c r="A66" s="3" t="s">
         <v>166</v>
       </c>
@@ -4623,7 +4632,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:3">
       <c r="A67" s="2" t="s">
         <v>169</v>
       </c>
@@ -4634,7 +4643,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:3">
       <c r="A68" s="3" t="s">
         <v>172</v>
       </c>
@@ -4645,7 +4654,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:3">
       <c r="A69" s="2" t="s">
         <v>175</v>
       </c>
@@ -4656,7 +4665,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:3">
       <c r="A70" s="3" t="s">
         <v>177</v>
       </c>
@@ -4667,7 +4676,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:3">
       <c r="A71" s="2" t="s">
         <v>180</v>
       </c>
@@ -4678,7 +4687,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:3">
       <c r="A72" s="3" t="s">
         <v>183</v>
       </c>
@@ -4689,7 +4698,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:3">
       <c r="A73" s="2" t="s">
         <v>186</v>
       </c>
@@ -4700,7 +4709,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:3">
       <c r="A74" s="3" t="s">
         <v>189</v>
       </c>
@@ -4711,7 +4720,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:3">
       <c r="A75" s="2" t="s">
         <v>192</v>
       </c>
@@ -4722,7 +4731,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:3">
       <c r="A76" s="3" t="s">
         <v>195</v>
       </c>
@@ -4733,7 +4742,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:3">
       <c r="A77" s="2" t="s">
         <v>198</v>
       </c>
@@ -4744,7 +4753,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:3">
       <c r="A78" s="3" t="s">
         <v>201</v>
       </c>
@@ -4755,7 +4764,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:3">
       <c r="A79" s="2" t="s">
         <v>203</v>
       </c>
@@ -4766,7 +4775,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:3">
       <c r="A80" s="3" t="s">
         <v>206</v>
       </c>
@@ -4777,7 +4786,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:3">
       <c r="A81" s="2" t="s">
         <v>209</v>
       </c>
@@ -4788,7 +4797,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:3">
       <c r="A82" s="3" t="s">
         <v>212</v>
       </c>
@@ -4799,7 +4808,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:3">
       <c r="A83" s="2" t="s">
         <v>215</v>
       </c>
@@ -4810,7 +4819,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:3">
       <c r="A84" s="3" t="s">
         <v>218</v>
       </c>
@@ -4821,7 +4830,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:3">
       <c r="A85" s="2" t="s">
         <v>220</v>
       </c>
@@ -4832,7 +4841,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:3">
       <c r="A86" s="3" t="s">
         <v>222</v>
       </c>
@@ -4843,7 +4852,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:3">
       <c r="A87" s="2" t="s">
         <v>224</v>
       </c>
@@ -4854,7 +4863,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:3">
       <c r="A88" s="3" t="s">
         <v>226</v>
       </c>
@@ -4865,7 +4874,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:3">
       <c r="A89" s="2" t="s">
         <v>228</v>
       </c>
@@ -4876,7 +4885,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:3">
       <c r="A90" s="3" t="s">
         <v>230</v>
       </c>
@@ -4887,7 +4896,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:3">
       <c r="A91" s="2" t="s">
         <v>232</v>
       </c>
@@ -4898,7 +4907,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:3">
       <c r="A92" s="3" t="s">
         <v>234</v>
       </c>
@@ -4909,7 +4918,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:3">
       <c r="A93" s="2" t="s">
         <v>237</v>
       </c>
@@ -4920,7 +4929,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:3">
       <c r="A94" s="3" t="s">
         <v>240</v>
       </c>
@@ -4931,7 +4940,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:3">
       <c r="A95" s="2" t="s">
         <v>243</v>
       </c>
@@ -4942,7 +4951,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:3">
       <c r="A96" s="3" t="s">
         <v>246</v>
       </c>
@@ -4953,7 +4962,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:3">
       <c r="A97" s="2" t="s">
         <v>249</v>
       </c>
@@ -4964,7 +4973,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:3">
       <c r="A98" s="3" t="s">
         <v>252</v>
       </c>
@@ -4975,7 +4984,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:3">
       <c r="A99" s="2" t="s">
         <v>255</v>
       </c>
@@ -4986,7 +4995,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:3">
       <c r="A100" s="3" t="s">
         <v>258</v>
       </c>
@@ -4997,7 +5006,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:3">
       <c r="A101" s="2" t="s">
         <v>261</v>
       </c>
@@ -5008,7 +5017,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:3">
       <c r="A102" s="3" t="s">
         <v>264</v>
       </c>
@@ -5019,7 +5028,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:3">
       <c r="A103" s="2" t="s">
         <v>267</v>
       </c>
@@ -5030,7 +5039,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:3">
       <c r="A104" s="3" t="s">
         <v>270</v>
       </c>
@@ -5041,7 +5050,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:3">
       <c r="A105" s="2" t="s">
         <v>273</v>
       </c>
@@ -5052,7 +5061,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:3">
       <c r="A106" s="3" t="s">
         <v>276</v>
       </c>
@@ -5063,7 +5072,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:3">
       <c r="A107" s="2" t="s">
         <v>279</v>
       </c>
@@ -5074,7 +5083,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:3">
       <c r="A108" s="3" t="s">
         <v>282</v>
       </c>
@@ -5085,7 +5094,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:3">
       <c r="A109" s="2" t="s">
         <v>284</v>
       </c>
@@ -5096,7 +5105,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:3">
       <c r="A110" s="3" t="s">
         <v>287</v>
       </c>
@@ -5107,7 +5116,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:3">
       <c r="A111" s="2" t="s">
         <v>290</v>
       </c>
@@ -5118,7 +5127,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:3">
       <c r="A112" s="3" t="s">
         <v>293</v>
       </c>
@@ -5129,7 +5138,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:3">
       <c r="A113" s="2" t="s">
         <v>296</v>
       </c>
@@ -5140,7 +5149,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:3">
       <c r="A114" s="3" t="s">
         <v>299</v>
       </c>
@@ -5151,7 +5160,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:3">
       <c r="A115" s="2" t="s">
         <v>302</v>
       </c>
@@ -5162,7 +5171,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:3">
       <c r="A116" s="2" t="s">
         <v>305</v>
       </c>
@@ -5173,7 +5182,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:3">
       <c r="A117" s="3" t="s">
         <v>308</v>
       </c>
@@ -5184,7 +5193,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:3">
       <c r="A118" s="2" t="s">
         <v>311</v>
       </c>
@@ -5195,7 +5204,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:3">
       <c r="A119" s="3" t="s">
         <v>314</v>
       </c>
@@ -5206,7 +5215,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:3">
       <c r="A120" s="2" t="s">
         <v>317</v>
       </c>
@@ -5217,7 +5226,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:3">
       <c r="A121" s="3" t="s">
         <v>319</v>
       </c>
@@ -5228,7 +5237,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:3">
       <c r="A122" s="2" t="s">
         <v>322</v>
       </c>
@@ -5239,7 +5248,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:3">
       <c r="A123" s="3" t="s">
         <v>325</v>
       </c>
@@ -5250,7 +5259,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:3">
       <c r="A124" s="2" t="s">
         <v>328</v>
       </c>
@@ -5261,7 +5270,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:3">
       <c r="A125" s="3" t="s">
         <v>331</v>
       </c>
@@ -5272,7 +5281,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:3">
       <c r="A126" s="2" t="s">
         <v>333</v>
       </c>
@@ -5283,7 +5292,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:3">
       <c r="A127" s="3" t="s">
         <v>336</v>
       </c>
@@ -5294,7 +5303,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:3">
       <c r="A128" s="2" t="s">
         <v>339</v>
       </c>
@@ -5305,7 +5314,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:3">
       <c r="A129" s="3" t="s">
         <v>341</v>
       </c>
@@ -5316,7 +5325,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:3">
       <c r="A130" s="2" t="s">
         <v>343</v>
       </c>
@@ -5327,7 +5336,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:3">
       <c r="A131" s="3" t="s">
         <v>345</v>
       </c>
@@ -5338,7 +5347,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:3">
       <c r="A132" s="2" t="s">
         <v>347</v>
       </c>
@@ -5349,7 +5358,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:3">
       <c r="A133" s="3" t="s">
         <v>349</v>
       </c>
@@ -5360,7 +5369,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:3">
       <c r="A134" s="2" t="s">
         <v>351</v>
       </c>
@@ -5371,7 +5380,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:3">
       <c r="A135" s="3" t="s">
         <v>353</v>
       </c>
@@ -5382,7 +5391,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:3">
       <c r="A136" s="2" t="s">
         <v>356</v>
       </c>
@@ -5393,7 +5402,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:3">
       <c r="A137" s="3" t="s">
         <v>359</v>
       </c>
@@ -5404,7 +5413,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:3">
       <c r="A138" s="2" t="s">
         <v>362</v>
       </c>
@@ -5415,7 +5424,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:3">
       <c r="A139" s="3" t="s">
         <v>364</v>
       </c>
@@ -5426,7 +5435,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:3">
       <c r="A140" s="2" t="s">
         <v>367</v>
       </c>
@@ -5437,7 +5446,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:3">
       <c r="A141" s="3" t="s">
         <v>369</v>
       </c>
@@ -5448,7 +5457,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:3">
       <c r="A142" s="2" t="s">
         <v>371</v>
       </c>
@@ -5459,7 +5468,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:3">
       <c r="A143" s="3" t="s">
         <v>374</v>
       </c>
@@ -5470,7 +5479,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:3">
       <c r="A144" s="2" t="s">
         <v>377</v>
       </c>
@@ -5481,7 +5490,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:3">
       <c r="A145" s="3" t="s">
         <v>380</v>
       </c>
@@ -5492,7 +5501,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:3">
       <c r="A146" s="2" t="s">
         <v>383</v>
       </c>
@@ -5503,7 +5512,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:3">
       <c r="A147" s="3" t="s">
         <v>386</v>
       </c>
@@ -5514,7 +5523,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:3">
       <c r="A148" s="2" t="s">
         <v>388</v>
       </c>
@@ -5525,7 +5534,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:3">
       <c r="A149" s="3" t="s">
         <v>391</v>
       </c>
@@ -5536,7 +5545,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:3">
       <c r="A150" s="2" t="s">
         <v>394</v>
       </c>
@@ -5547,7 +5556,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:3">
       <c r="A151" s="3" t="s">
         <v>396</v>
       </c>
@@ -5558,7 +5567,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:3">
       <c r="A152" s="2" t="s">
         <v>399</v>
       </c>
@@ -5569,7 +5578,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:3">
       <c r="A153" s="3" t="s">
         <v>401</v>
       </c>
@@ -5580,7 +5589,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:3">
       <c r="A154" s="2" t="s">
         <v>404</v>
       </c>
@@ -5591,7 +5600,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:3">
       <c r="A155" s="3" t="s">
         <v>406</v>
       </c>
@@ -5602,7 +5611,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:3">
       <c r="A156" s="2" t="s">
         <v>409</v>
       </c>
@@ -5613,7 +5622,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:3">
       <c r="A157" s="3" t="s">
         <v>411</v>
       </c>
@@ -5624,7 +5633,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:3">
       <c r="A158" s="2" t="s">
         <v>414</v>
       </c>
@@ -5635,7 +5644,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:3">
       <c r="A159" s="3" t="s">
         <v>417</v>
       </c>
@@ -5646,7 +5655,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:3">
       <c r="A160" s="2" t="s">
         <v>419</v>
       </c>
@@ -5657,7 +5666,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:3">
       <c r="A161" s="3" t="s">
         <v>422</v>
       </c>
@@ -5668,7 +5677,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:3">
       <c r="A162" s="2" t="s">
         <v>425</v>
       </c>
@@ -5679,7 +5688,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:3">
       <c r="A163" s="3" t="s">
         <v>428</v>
       </c>
@@ -5690,7 +5699,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:3">
       <c r="A164" s="2" t="s">
         <v>431</v>
       </c>
@@ -5701,7 +5710,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:3">
       <c r="A165" s="3" t="s">
         <v>434</v>
       </c>
@@ -5712,7 +5721,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:3">
       <c r="A166" s="2" t="s">
         <v>437</v>
       </c>
@@ -5723,7 +5732,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:3">
       <c r="A167" s="3" t="s">
         <v>439</v>
       </c>
@@ -5734,7 +5743,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:3">
       <c r="A168" s="2" t="s">
         <v>442</v>
       </c>
@@ -5745,7 +5754,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:3">
       <c r="A169" s="3" t="s">
         <v>445</v>
       </c>
@@ -5756,7 +5765,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:3">
       <c r="A170" s="2" t="s">
         <v>448</v>
       </c>
@@ -5767,7 +5776,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:3">
       <c r="A171" s="3" t="s">
         <v>451</v>
       </c>
@@ -5778,7 +5787,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:3">
       <c r="A172" s="2" t="s">
         <v>454</v>
       </c>
@@ -5789,7 +5798,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:3">
       <c r="A173" s="3" t="s">
         <v>457</v>
       </c>
@@ -5800,7 +5809,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:3">
       <c r="A174" s="2" t="s">
         <v>460</v>
       </c>
@@ -5811,7 +5820,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:3">
       <c r="A175" s="3" t="s">
         <v>463</v>
       </c>
@@ -5822,7 +5831,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:3">
       <c r="A176" s="2" t="s">
         <v>466</v>
       </c>
@@ -5833,7 +5842,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:3">
       <c r="A177" s="3" t="s">
         <v>469</v>
       </c>
@@ -5844,7 +5853,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:3">
       <c r="A178" s="2" t="s">
         <v>472</v>
       </c>
@@ -5855,7 +5864,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:3">
       <c r="A179" s="3" t="s">
         <v>475</v>
       </c>
@@ -5866,7 +5875,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:3">
       <c r="A180" s="2" t="s">
         <v>478</v>
       </c>
@@ -5877,7 +5886,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:3">
       <c r="A181" s="3" t="s">
         <v>481</v>
       </c>
@@ -5888,7 +5897,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:3">
       <c r="A182" s="2" t="s">
         <v>483</v>
       </c>
@@ -5899,7 +5908,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:3">
       <c r="A183" s="3" t="s">
         <v>486</v>
       </c>
@@ -5910,7 +5919,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:3">
       <c r="A184" s="2" t="s">
         <v>488</v>
       </c>
@@ -5921,7 +5930,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:3">
       <c r="A185" s="3" t="s">
         <v>491</v>
       </c>
@@ -5932,7 +5941,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:3">
       <c r="A186" s="2" t="s">
         <v>494</v>
       </c>
@@ -5943,7 +5952,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:3">
       <c r="A187" s="3" t="s">
         <v>497</v>
       </c>
@@ -5954,7 +5963,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:3">
       <c r="A188" s="2" t="s">
         <v>499</v>
       </c>
@@ -5965,7 +5974,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:3">
       <c r="A189" s="3" t="s">
         <v>502</v>
       </c>
@@ -5976,7 +5985,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:3">
       <c r="A190" s="2" t="s">
         <v>505</v>
       </c>
@@ -5987,7 +5996,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:3">
       <c r="A191" s="3" t="s">
         <v>508</v>
       </c>
@@ -5998,7 +6007,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:3">
       <c r="A192" s="2" t="s">
         <v>511</v>
       </c>
@@ -6009,7 +6018,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:3">
       <c r="A193" s="3" t="s">
         <v>514</v>
       </c>
@@ -6020,7 +6029,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:3">
       <c r="A194" s="2" t="s">
         <v>517</v>
       </c>
@@ -6031,7 +6040,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:3">
       <c r="A195" s="3" t="s">
         <v>520</v>
       </c>
@@ -6042,7 +6051,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:3">
       <c r="A196" s="2" t="s">
         <v>523</v>
       </c>
@@ -6053,7 +6062,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:3">
       <c r="A197" s="3" t="s">
         <v>525</v>
       </c>
@@ -6064,7 +6073,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:3">
       <c r="A198" s="2" t="s">
         <v>528</v>
       </c>
@@ -6075,7 +6084,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:3">
       <c r="A199" s="3" t="s">
         <v>531</v>
       </c>
@@ -6086,7 +6095,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:3">
       <c r="A200" s="2" t="s">
         <v>534</v>
       </c>
@@ -6097,7 +6106,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:3">
       <c r="A201" s="3" t="s">
         <v>537</v>
       </c>
@@ -6108,7 +6117,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:3">
       <c r="A202" s="2" t="s">
         <v>540</v>
       </c>
@@ -6119,7 +6128,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:3">
       <c r="A203" s="3" t="s">
         <v>542</v>
       </c>
@@ -6130,7 +6139,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:3">
       <c r="A204" s="2" t="s">
         <v>544</v>
       </c>
@@ -6141,7 +6150,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="1:3">
       <c r="A205" s="3" t="s">
         <v>547</v>
       </c>
@@ -6152,7 +6161,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:3">
       <c r="A206" s="2" t="s">
         <v>549</v>
       </c>
@@ -6163,7 +6172,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:3">
       <c r="A207" s="3" t="s">
         <v>552</v>
       </c>
@@ -6174,7 +6183,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="1:3">
       <c r="A208" s="2" t="s">
         <v>555</v>
       </c>
@@ -6185,7 +6194,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="1:3">
       <c r="A209" s="3" t="s">
         <v>558</v>
       </c>
@@ -6196,7 +6205,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="1:3">
       <c r="A210" s="2" t="s">
         <v>561</v>
       </c>
@@ -6207,7 +6216,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="1:3">
       <c r="A211" s="3" t="s">
         <v>564</v>
       </c>
@@ -6218,7 +6227,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="1:3">
       <c r="A212" s="2" t="s">
         <v>566</v>
       </c>
@@ -6229,7 +6238,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="1:3">
       <c r="A213" s="3" t="s">
         <v>569</v>
       </c>
@@ -6240,7 +6249,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="1:3">
       <c r="A214" s="2" t="s">
         <v>571</v>
       </c>
@@ -6251,7 +6260,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="1:3">
       <c r="A215" s="3" t="s">
         <v>574</v>
       </c>
@@ -6262,7 +6271,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="1:3">
       <c r="A216" s="2" t="s">
         <v>577</v>
       </c>
@@ -6273,7 +6282,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="1:3">
       <c r="A217" s="3" t="s">
         <v>580</v>
       </c>
@@ -6284,7 +6293,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="1:3">
       <c r="A218" s="2" t="s">
         <v>583</v>
       </c>
@@ -6295,7 +6304,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="1:3">
       <c r="A219" s="3" t="s">
         <v>586</v>
       </c>
@@ -6306,7 +6315,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" spans="1:3">
       <c r="A220" s="2" t="s">
         <v>589</v>
       </c>
@@ -6317,7 +6326,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" spans="1:3">
       <c r="A221" s="3" t="s">
         <v>592</v>
       </c>
@@ -6328,7 +6337,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" spans="1:3">
       <c r="A222" s="2" t="s">
         <v>594</v>
       </c>
@@ -6339,7 +6348,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" spans="1:3">
       <c r="A223" s="3" t="s">
         <v>597</v>
       </c>
@@ -6350,7 +6359,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" spans="1:3">
       <c r="A224" s="2" t="s">
         <v>599</v>
       </c>
@@ -6361,7 +6370,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" spans="1:3">
       <c r="A225" s="3" t="s">
         <v>602</v>
       </c>
@@ -6372,7 +6381,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" spans="1:3">
       <c r="A226" s="2" t="s">
         <v>604</v>
       </c>
@@ -6383,7 +6392,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="1:3">
       <c r="A227" s="3" t="s">
         <v>606</v>
       </c>
@@ -6394,7 +6403,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" spans="1:3">
       <c r="A228" s="2" t="s">
         <v>609</v>
       </c>
@@ -6405,7 +6414,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" spans="1:3">
       <c r="A229" s="3" t="s">
         <v>611</v>
       </c>
@@ -6416,7 +6425,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" spans="1:3">
       <c r="A230" s="2" t="s">
         <v>614</v>
       </c>
@@ -6427,7 +6436,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="1:3">
       <c r="A231" s="3" t="s">
         <v>617</v>
       </c>
@@ -6438,7 +6447,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="1:3">
       <c r="A232" s="2" t="s">
         <v>619</v>
       </c>
@@ -6449,7 +6458,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" spans="1:3">
       <c r="A233" s="3" t="s">
         <v>622</v>
       </c>
@@ -6460,7 +6469,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="1:3">
       <c r="A234" s="2" t="s">
         <v>624</v>
       </c>
@@ -6471,7 +6480,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" spans="1:3">
       <c r="A235" s="2" t="s">
         <v>626</v>
       </c>
@@ -6482,7 +6491,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="1:3">
       <c r="A236" s="3" t="s">
         <v>628</v>
       </c>
@@ -6493,7 +6502,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" spans="1:3">
       <c r="A237" s="2" t="s">
         <v>630</v>
       </c>
@@ -6504,7 +6513,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" spans="1:3">
       <c r="A238" s="3" t="s">
         <v>632</v>
       </c>
@@ -6515,7 +6524,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" spans="1:3">
       <c r="A239" s="2" t="s">
         <v>635</v>
       </c>
@@ -6526,7 +6535,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="1:3">
       <c r="A240" s="3" t="s">
         <v>638</v>
       </c>
@@ -6537,7 +6546,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="1:3">
       <c r="A241" s="2" t="s">
         <v>640</v>
       </c>
@@ -6548,7 +6557,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" spans="1:3">
       <c r="A242" s="3" t="s">
         <v>643</v>
       </c>
@@ -6559,7 +6568,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" spans="1:3">
       <c r="A243" s="2" t="s">
         <v>645</v>
       </c>
@@ -6570,7 +6579,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" spans="1:3">
       <c r="A244" s="3" t="s">
         <v>648</v>
       </c>
@@ -6581,7 +6590,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" spans="1:3">
       <c r="A245" s="2" t="s">
         <v>650</v>
       </c>
@@ -6592,7 +6601,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" spans="1:3">
       <c r="A246" s="3" t="s">
         <v>652</v>
       </c>
@@ -6603,7 +6612,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" spans="1:3">
       <c r="A247" s="2" t="s">
         <v>655</v>
       </c>
@@ -6614,7 +6623,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" spans="1:3">
       <c r="A248" s="3" t="s">
         <v>658</v>
       </c>
@@ -6625,7 +6634,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" spans="1:3">
       <c r="A249" s="2" t="s">
         <v>661</v>
       </c>
@@ -6636,7 +6645,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" spans="1:3">
       <c r="A250" s="3" t="s">
         <v>664</v>
       </c>
@@ -6647,7 +6656,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" spans="1:3">
       <c r="A251" s="2" t="s">
         <v>667</v>
       </c>
@@ -6658,7 +6667,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" spans="1:3">
       <c r="A252" s="3" t="s">
         <v>670</v>
       </c>
@@ -6669,7 +6678,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" spans="1:3">
       <c r="A253" s="2" t="s">
         <v>672</v>
       </c>
@@ -6680,7 +6689,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" spans="1:3">
       <c r="A254" s="3" t="s">
         <v>674</v>
       </c>
@@ -6691,7 +6700,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" spans="1:3">
       <c r="A255" s="2" t="s">
         <v>677</v>
       </c>
@@ -6702,7 +6711,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" spans="1:3">
       <c r="A256" s="3" t="s">
         <v>679</v>
       </c>
@@ -6713,7 +6722,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" spans="1:3">
       <c r="A257" s="2" t="s">
         <v>682</v>
       </c>
@@ -6724,7 +6733,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" spans="1:3">
       <c r="A258" s="3" t="s">
         <v>684</v>
       </c>
@@ -6735,7 +6744,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" spans="1:3">
       <c r="A259" s="2" t="s">
         <v>686</v>
       </c>
@@ -6746,7 +6755,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" spans="1:3">
       <c r="A260" s="3" t="s">
         <v>688</v>
       </c>
@@ -6757,7 +6766,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" spans="1:3">
       <c r="A261" s="2" t="s">
         <v>690</v>
       </c>
@@ -6768,7 +6777,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" spans="1:3">
       <c r="A262" s="3" t="s">
         <v>693</v>
       </c>
@@ -6779,7 +6788,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" spans="1:3">
       <c r="A263" s="2" t="s">
         <v>696</v>
       </c>
@@ -6790,7 +6799,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" spans="1:3">
       <c r="A264" s="3" t="s">
         <v>699</v>
       </c>
@@ -6801,7 +6810,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" spans="1:3">
       <c r="A265" s="2" t="s">
         <v>702</v>
       </c>
@@ -6812,7 +6821,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" spans="1:3">
       <c r="A266" s="3" t="s">
         <v>705</v>
       </c>
@@ -6823,7 +6832,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" spans="1:3">
       <c r="A267" s="2" t="s">
         <v>708</v>
       </c>
@@ -6834,7 +6843,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" spans="1:3">
       <c r="A268" s="3" t="s">
         <v>710</v>
       </c>
@@ -6845,7 +6854,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" spans="1:3">
       <c r="A269" s="2" t="s">
         <v>712</v>
       </c>
@@ -6856,7 +6865,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" spans="1:3">
       <c r="A270" s="3" t="s">
         <v>715</v>
       </c>
@@ -6867,7 +6876,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" spans="1:3">
       <c r="A271" s="2" t="s">
         <v>718</v>
       </c>
@@ -6878,7 +6887,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" spans="1:3">
       <c r="A272" s="3" t="s">
         <v>721</v>
       </c>
@@ -6889,7 +6898,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" spans="1:3">
       <c r="A273" s="2" t="s">
         <v>724</v>
       </c>
@@ -6900,7 +6909,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" spans="1:3">
       <c r="A274" s="3" t="s">
         <v>726</v>
       </c>
@@ -6911,7 +6920,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" spans="1:3">
       <c r="A275" s="2" t="s">
         <v>728</v>
       </c>
@@ -6922,7 +6931,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" spans="1:3">
       <c r="A276" s="3" t="s">
         <v>731</v>
       </c>
@@ -6933,7 +6942,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" spans="1:3">
       <c r="A277" s="2" t="s">
         <v>734</v>
       </c>
@@ -6944,7 +6953,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" spans="1:3">
       <c r="A278" s="3" t="s">
         <v>736</v>
       </c>
@@ -6955,7 +6964,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="279">
+    <row r="279" spans="1:3">
       <c r="A279" s="2" t="s">
         <v>739</v>
       </c>
@@ -6966,7 +6975,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="280">
+    <row r="280" spans="1:3">
       <c r="A280" s="3" t="s">
         <v>741</v>
       </c>
@@ -6977,7 +6986,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="281">
+    <row r="281" spans="1:3">
       <c r="A281" s="2" t="s">
         <v>744</v>
       </c>
@@ -6988,7 +6997,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" spans="1:3">
       <c r="A282" s="3" t="s">
         <v>747</v>
       </c>
@@ -6999,7 +7008,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="283">
+    <row r="283" spans="1:3">
       <c r="A283" s="2" t="s">
         <v>749</v>
       </c>
@@ -7010,7 +7019,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="284">
+    <row r="284" spans="1:3">
       <c r="A284" s="3" t="s">
         <v>752</v>
       </c>
@@ -7021,7 +7030,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" spans="1:3">
       <c r="A285" s="3" t="s">
         <v>755</v>
       </c>
@@ -7032,7 +7041,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" spans="1:3">
       <c r="A286" s="2" t="s">
         <v>757</v>
       </c>
@@ -7043,7 +7052,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" spans="1:3">
       <c r="A287" s="3" t="s">
         <v>759</v>
       </c>
@@ -7054,7 +7063,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" spans="1:3">
       <c r="A288" s="2" t="s">
         <v>762</v>
       </c>
@@ -7065,7 +7074,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" spans="1:3">
       <c r="A289" s="3" t="s">
         <v>765</v>
       </c>
@@ -7076,7 +7085,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" spans="1:3">
       <c r="A290" s="2" t="s">
         <v>768</v>
       </c>
@@ -7087,7 +7096,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" spans="1:3">
       <c r="A291" s="3" t="s">
         <v>771</v>
       </c>
@@ -7098,7 +7107,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" spans="1:3">
       <c r="A292" s="2" t="s">
         <v>773</v>
       </c>
@@ -7109,7 +7118,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" spans="1:3">
       <c r="A293" s="3" t="s">
         <v>775</v>
       </c>
@@ -7120,7 +7129,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="294">
+    <row r="294" spans="1:3">
       <c r="A294" s="2" t="s">
         <v>778</v>
       </c>
@@ -7131,7 +7140,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" spans="1:3">
       <c r="A295" s="3" t="s">
         <v>780</v>
       </c>
@@ -7142,7 +7151,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="296">
+    <row r="296" spans="1:3">
       <c r="A296" s="3" t="s">
         <v>782</v>
       </c>
@@ -7153,7 +7162,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="297">
+    <row r="297" spans="1:3">
       <c r="A297" s="2" t="s">
         <v>784</v>
       </c>
@@ -7164,7 +7173,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" spans="1:3">
       <c r="A298" s="3" t="s">
         <v>787</v>
       </c>
@@ -7175,7 +7184,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" spans="1:3">
       <c r="A299" s="2" t="s">
         <v>789</v>
       </c>
@@ -7186,7 +7195,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="300">
+    <row r="300" spans="1:3">
       <c r="A300" s="3" t="s">
         <v>792</v>
       </c>
@@ -7197,7 +7206,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="301">
+    <row r="301" spans="1:3">
       <c r="A301" s="2" t="s">
         <v>794</v>
       </c>
@@ -7208,7 +7217,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="302">
+    <row r="302" spans="1:3">
       <c r="A302" s="3" t="s">
         <v>797</v>
       </c>
@@ -7219,4365 +7228,3271 @@
         <v>798</v>
       </c>
     </row>
-    <row r="303">
+    <row r="303" spans="1:3">
       <c r="A303" s="2" t="s">
         <v>799</v>
       </c>
       <c r="B303" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C303" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="C303" s="2" t="s">
+    </row>
+    <row r="304" spans="1:3">
+      <c r="A304" s="3" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="3" t="s">
+      <c r="B304" s="3" t="s">
         <v>802</v>
       </c>
-      <c r="B304" s="3" t="s">
+      <c r="C304" s="3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3">
+      <c r="A305" s="2" t="s">
         <v>803</v>
       </c>
-      <c r="C304" s="3" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="s">
+      <c r="B305" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="B305" s="2" t="s">
+      <c r="C305" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3">
+      <c r="A306" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="C305" s="2" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="3" t="s">
+      <c r="B306" s="3" t="s">
         <v>806</v>
       </c>
-      <c r="B306" s="3" t="s">
+      <c r="C306" s="3" t="s">
         <v>807</v>
       </c>
-      <c r="C306" s="3" t="s">
+    </row>
+    <row r="307" spans="1:3">
+      <c r="A307" s="2" t="s">
         <v>808</v>
       </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="2" t="s">
+      <c r="B307" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="B307" s="2" t="s">
+      <c r="C307" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3">
+      <c r="A308" s="3" t="s">
         <v>810</v>
       </c>
-      <c r="C307" s="2" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="3" t="s">
+      <c r="B308" s="3" t="s">
         <v>811</v>
       </c>
-      <c r="B308" s="3" t="s">
+      <c r="C308" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="C308" s="3" t="s">
+    </row>
+    <row r="309" spans="1:3">
+      <c r="A309" s="2" t="s">
         <v>813</v>
       </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="2" t="s">
+      <c r="B309" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="B309" s="2" t="s">
+      <c r="C309" s="2" t="s">
         <v>815</v>
       </c>
-      <c r="C309" s="2" t="s">
+    </row>
+    <row r="310" spans="1:3">
+      <c r="A310" s="3" t="s">
         <v>816</v>
       </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="3" t="s">
+      <c r="B310" s="3" t="s">
         <v>817</v>
       </c>
-      <c r="B310" s="3" t="s">
+      <c r="C310" s="3" t="s">
         <v>818</v>
       </c>
-      <c r="C310" s="3" t="s">
+    </row>
+    <row r="311" spans="1:3">
+      <c r="A311" s="2" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="2" t="s">
+      <c r="B311" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="B311" s="2" t="s">
+      <c r="C311" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="C311" s="2" t="s">
+    </row>
+    <row r="312" spans="1:3">
+      <c r="A312" s="3" t="s">
         <v>822</v>
       </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="3" t="s">
+      <c r="B312" s="3" t="s">
         <v>823</v>
       </c>
-      <c r="B312" s="3" t="s">
+      <c r="C312" s="3" t="s">
         <v>824</v>
       </c>
-      <c r="C312" s="3" t="s">
+    </row>
+    <row r="313" spans="1:3">
+      <c r="A313" s="3" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="3" t="s">
+      <c r="B313" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="B313" s="3" t="s">
+      <c r="C313" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="C313" s="3" t="s">
+    </row>
+    <row r="314" spans="1:3">
+      <c r="A314" s="2" t="s">
         <v>828</v>
       </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="2" t="s">
+      <c r="B314" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="B314" s="2" t="s">
+      <c r="C314" s="2" t="s">
         <v>830</v>
       </c>
-      <c r="C314" s="2" t="s">
+    </row>
+    <row r="315" spans="1:3">
+      <c r="A315" s="3" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="3" t="s">
+      <c r="B315" s="3" t="s">
         <v>832</v>
       </c>
-      <c r="B315" s="3" t="s">
+      <c r="C315" s="3" t="s">
         <v>833</v>
       </c>
-      <c r="C315" s="3" t="s">
+    </row>
+    <row r="316" spans="1:3">
+      <c r="A316" s="2" t="s">
         <v>834</v>
       </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2" t="s">
+      <c r="B316" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="B316" s="2" t="s">
+      <c r="C316" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="C316" s="2" t="s">
+    </row>
+    <row r="317" spans="1:3">
+      <c r="A317" s="3" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="3" t="s">
+      <c r="B317" s="3" t="s">
         <v>838</v>
       </c>
-      <c r="B317" s="3" t="s">
+      <c r="C317" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="C317" s="3" t="s">
+    </row>
+    <row r="318" spans="1:3">
+      <c r="A318" s="2" t="s">
         <v>840</v>
       </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="2" t="s">
+      <c r="B318" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="B318" s="2" t="s">
+      <c r="C318" s="2" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3">
+      <c r="A319" s="3" t="s">
         <v>842</v>
       </c>
-      <c r="C318" s="2" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="3" t="s">
+      <c r="B319" s="3" t="s">
         <v>843</v>
       </c>
-      <c r="B319" s="3" t="s">
+      <c r="C319" s="3" t="s">
         <v>844</v>
       </c>
-      <c r="C319" s="3" t="s">
+    </row>
+    <row r="320" spans="1:3">
+      <c r="A320" s="2" t="s">
         <v>845</v>
       </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="2" t="s">
+      <c r="B320" s="2" t="s">
         <v>846</v>
       </c>
-      <c r="B320" s="2" t="s">
+      <c r="C320" s="2" t="s">
         <v>847</v>
       </c>
-      <c r="C320" s="2" t="s">
+    </row>
+    <row r="321" spans="1:3">
+      <c r="A321" s="3" t="s">
         <v>848</v>
       </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="3" t="s">
+      <c r="B321" s="3" t="s">
         <v>849</v>
       </c>
-      <c r="B321" s="3" t="s">
+      <c r="C321" s="3" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3">
+      <c r="A322" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="C321" s="3" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="2" t="s">
+      <c r="B322" s="2" t="s">
         <v>851</v>
       </c>
-      <c r="B322" s="2" t="s">
+      <c r="C322" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3">
+      <c r="A323" s="3" t="s">
         <v>852</v>
       </c>
-      <c r="C322" s="2" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="3" t="s">
+      <c r="B323" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="B323" s="3" t="s">
+      <c r="C323" s="3" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
+      <c r="A324" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="C323" s="3" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="2" t="s">
+      <c r="B324" s="2" t="s">
         <v>855</v>
       </c>
-      <c r="B324" s="2" t="s">
+      <c r="C324" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="C324" s="2" t="s">
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325" s="3" t="s">
         <v>857</v>
       </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="3" t="s">
+      <c r="B325" s="3" t="s">
         <v>858</v>
       </c>
-      <c r="B325" s="3" t="s">
+      <c r="C325" s="3" t="s">
         <v>859</v>
       </c>
-      <c r="C325" s="3" t="s">
+    </row>
+    <row r="326" spans="1:3">
+      <c r="A326" s="2" t="s">
         <v>860</v>
       </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="2" t="s">
+      <c r="B326" s="2" t="s">
         <v>861</v>
       </c>
-      <c r="B326" s="2" t="s">
+      <c r="C326" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="C326" s="2" t="s">
+    </row>
+    <row r="327" spans="1:3">
+      <c r="A327" s="2" t="s">
         <v>863</v>
       </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="2" t="s">
+      <c r="B327" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="B327" s="2" t="s">
+      <c r="C327" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="C327" s="2" t="s">
+    </row>
+    <row r="328" spans="1:3">
+      <c r="A328" s="3" t="s">
         <v>866</v>
       </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="3" t="s">
+      <c r="B328" s="3" t="s">
         <v>867</v>
       </c>
-      <c r="B328" s="3" t="s">
+      <c r="C328" s="3" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3">
+      <c r="A329" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="C328" s="3" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="2" t="s">
+      <c r="B329" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="B329" s="2" t="s">
+      <c r="C329" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="C329" s="2" t="s">
+    </row>
+    <row r="330" spans="1:3">
+      <c r="A330" s="3" t="s">
         <v>871</v>
       </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="3" t="s">
+      <c r="B330" s="3" t="s">
         <v>872</v>
       </c>
-      <c r="B330" s="3" t="s">
+      <c r="C330" s="3" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3">
+      <c r="A331" s="2" t="s">
         <v>873</v>
       </c>
-      <c r="C330" s="3" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="2" t="s">
+      <c r="B331" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="B331" s="2" t="s">
+      <c r="C331" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="C331" s="2" t="s">
+    </row>
+    <row r="332" spans="1:3">
+      <c r="A332" s="3" t="s">
         <v>876</v>
       </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="3" t="s">
+      <c r="B332" s="3" t="s">
         <v>877</v>
       </c>
-      <c r="B332" s="3" t="s">
+      <c r="C332" s="3" t="s">
         <v>878</v>
       </c>
-      <c r="C332" s="3" t="s">
+    </row>
+    <row r="333" spans="1:3">
+      <c r="A333" s="2" t="s">
         <v>879</v>
       </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="2" t="s">
+      <c r="B333" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="B333" s="2" t="s">
+      <c r="C333" s="2" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3">
+      <c r="A334" s="3" t="s">
         <v>881</v>
       </c>
-      <c r="C333" s="2" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="3" t="s">
+      <c r="B334" s="3" t="s">
         <v>882</v>
       </c>
-      <c r="B334" s="3" t="s">
+      <c r="C334" s="3" t="s">
         <v>883</v>
       </c>
-      <c r="C334" s="3" t="s">
+    </row>
+    <row r="335" spans="1:3">
+      <c r="A335" s="2" t="s">
         <v>884</v>
       </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="2" t="s">
+      <c r="B335" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="B335" s="2" t="s">
+      <c r="C335" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="C335" s="2" t="s">
+    </row>
+    <row r="336" spans="1:3">
+      <c r="A336" s="3" t="s">
         <v>887</v>
       </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="3" t="s">
+      <c r="B336" s="3" t="s">
         <v>888</v>
       </c>
-      <c r="B336" s="3" t="s">
+      <c r="C336" s="3" t="s">
         <v>889</v>
       </c>
-      <c r="C336" s="3" t="s">
+    </row>
+    <row r="337" spans="1:3">
+      <c r="A337" s="2" t="s">
         <v>890</v>
       </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="2" t="s">
+      <c r="B337" s="2" t="s">
         <v>891</v>
       </c>
-      <c r="B337" s="2" t="s">
+      <c r="C337" s="2" t="s">
         <v>892</v>
       </c>
-      <c r="C337" s="2" t="s">
+    </row>
+    <row r="338" spans="1:3">
+      <c r="A338" s="3" t="s">
         <v>893</v>
       </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="3" t="s">
+      <c r="B338" s="3" t="s">
         <v>894</v>
       </c>
-      <c r="B338" s="3" t="s">
+      <c r="C338" s="3" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="A339" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="C338" s="3" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="2" t="s">
+      <c r="B339" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="B339" s="2" t="s">
+      <c r="C339" s="2" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340" s="3" t="s">
         <v>897</v>
       </c>
-      <c r="C339" s="2" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="3" t="s">
+      <c r="B340" s="3" t="s">
         <v>898</v>
       </c>
-      <c r="B340" s="3" t="s">
+      <c r="C340" s="3" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3">
+      <c r="A341" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="C340" s="3" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="2" t="s">
+      <c r="B341" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="B341" s="2" t="s">
+      <c r="C341" s="2" t="s">
         <v>901</v>
       </c>
-      <c r="C341" s="2" t="s">
+    </row>
+    <row r="342" spans="1:3">
+      <c r="A342" s="3" t="s">
         <v>902</v>
       </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="3" t="s">
+      <c r="B342" s="3" t="s">
         <v>903</v>
       </c>
-      <c r="B342" s="3" t="s">
+      <c r="C342" s="3" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3">
+      <c r="A343" s="2" t="s">
         <v>904</v>
       </c>
-      <c r="C342" s="3" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="2" t="s">
+      <c r="B343" s="2" t="s">
         <v>905</v>
       </c>
-      <c r="B343" s="2" t="s">
+      <c r="C343" s="2" t="s">
         <v>906</v>
       </c>
-      <c r="C343" s="2" t="s">
+    </row>
+    <row r="344" spans="1:3">
+      <c r="A344" s="3" t="s">
         <v>907</v>
       </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="3" t="s">
+      <c r="B344" s="3" t="s">
         <v>908</v>
       </c>
-      <c r="B344" s="3" t="s">
+      <c r="C344" s="3" t="s">
         <v>909</v>
       </c>
-      <c r="C344" s="3" t="s">
+    </row>
+    <row r="345" spans="1:3">
+      <c r="A345" s="2" t="s">
         <v>910</v>
       </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="2" t="s">
+      <c r="B345" s="2" t="s">
         <v>911</v>
       </c>
-      <c r="B345" s="2" t="s">
+      <c r="C345" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="C345" s="2" t="s">
+    </row>
+    <row r="346" spans="1:3">
+      <c r="A346" s="3" t="s">
         <v>913</v>
       </c>
-    </row>
-    <row r="346">
-      <c r="A346" s="3" t="s">
+      <c r="B346" s="3" t="s">
         <v>914</v>
       </c>
-      <c r="B346" s="3" t="s">
+      <c r="C346" s="3" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3">
+      <c r="A347" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="C346" s="3" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="2" t="s">
+      <c r="B347" s="2" t="s">
         <v>916</v>
       </c>
-      <c r="B347" s="2" t="s">
+      <c r="C347" s="2" t="s">
         <v>917</v>
       </c>
-      <c r="C347" s="2" t="s">
+    </row>
+    <row r="348" spans="1:3">
+      <c r="A348" s="3" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="3" t="s">
+      <c r="B348" s="3" t="s">
         <v>919</v>
       </c>
-      <c r="B348" s="3" t="s">
+      <c r="C348" s="3" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3">
+      <c r="A349" s="2" t="s">
         <v>920</v>
       </c>
-      <c r="C348" s="3" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" s="2" t="s">
+      <c r="B349" s="2" t="s">
         <v>921</v>
       </c>
-      <c r="B349" s="2" t="s">
+      <c r="C349" s="2" t="s">
         <v>922</v>
       </c>
-      <c r="C349" s="2" t="s">
+    </row>
+    <row r="350" spans="1:3">
+      <c r="A350" s="3" t="s">
         <v>923</v>
       </c>
-    </row>
-    <row r="350">
-      <c r="A350" s="3" t="s">
+      <c r="B350" s="3" t="s">
         <v>924</v>
       </c>
-      <c r="B350" s="3" t="s">
+      <c r="C350" s="3" t="s">
         <v>925</v>
       </c>
-      <c r="C350" s="3" t="s">
+    </row>
+    <row r="351" spans="1:3">
+      <c r="A351" s="2" t="s">
         <v>926</v>
       </c>
-    </row>
-    <row r="351">
-      <c r="A351" s="2" t="s">
+      <c r="B351" s="2" t="s">
         <v>927</v>
       </c>
-      <c r="B351" s="2" t="s">
+      <c r="C351" s="2" t="s">
         <v>928</v>
       </c>
-      <c r="C351" s="2" t="s">
+    </row>
+    <row r="352" spans="1:3">
+      <c r="A352" s="3" t="s">
         <v>929</v>
       </c>
-    </row>
-    <row r="352">
-      <c r="A352" s="3" t="s">
+      <c r="B352" s="3" t="s">
         <v>930</v>
       </c>
-      <c r="B352" s="3" t="s">
+      <c r="C352" s="3" t="s">
         <v>931</v>
       </c>
-      <c r="C352" s="3" t="s">
+    </row>
+    <row r="353" spans="1:3">
+      <c r="A353" s="2" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="2" t="s">
+      <c r="B353" s="2" t="s">
         <v>933</v>
       </c>
-      <c r="B353" s="2" t="s">
+      <c r="C353" s="2" t="s">
         <v>934</v>
       </c>
-      <c r="C353" s="2" t="s">
+    </row>
+    <row r="354" spans="1:3">
+      <c r="A354" s="3" t="s">
         <v>935</v>
       </c>
-    </row>
-    <row r="354">
-      <c r="A354" s="3" t="s">
+      <c r="B354" s="3" t="s">
         <v>936</v>
       </c>
-      <c r="B354" s="3" t="s">
+      <c r="C354" s="3" t="s">
         <v>937</v>
       </c>
-      <c r="C354" s="3" t="s">
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355" s="2" t="s">
         <v>938</v>
       </c>
-    </row>
-    <row r="355">
-      <c r="A355" s="2" t="s">
+      <c r="B355" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="B355" s="2" t="s">
+      <c r="C355" s="2" t="s">
         <v>940</v>
       </c>
-      <c r="C355" s="2" t="s">
+    </row>
+    <row r="356" spans="1:3">
+      <c r="A356" s="3" t="s">
         <v>941</v>
       </c>
-    </row>
-    <row r="356">
-      <c r="A356" s="3" t="s">
+      <c r="B356" s="3" t="s">
         <v>942</v>
       </c>
-      <c r="B356" s="3" t="s">
+      <c r="C356" s="3" t="s">
         <v>943</v>
       </c>
-      <c r="C356" s="3" t="s">
+    </row>
+    <row r="357" spans="1:3">
+      <c r="A357" s="2" t="s">
         <v>944</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" s="2" t="s">
-        <v>945</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>636</v>
       </c>
       <c r="C357" s="2" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3">
+      <c r="A358" s="3" t="s">
         <v>946</v>
       </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="3" t="s">
+      <c r="B358" s="3" t="s">
         <v>947</v>
       </c>
-      <c r="B358" s="3" t="s">
+      <c r="C358" s="3" t="s">
         <v>948</v>
       </c>
-      <c r="C358" s="3" t="s">
+    </row>
+    <row r="359" spans="1:3">
+      <c r="A359" s="2" t="s">
         <v>949</v>
       </c>
-    </row>
-    <row r="359">
-      <c r="A359" s="2" t="s">
+      <c r="B359" s="2" t="s">
         <v>950</v>
       </c>
-      <c r="B359" s="2" t="s">
+      <c r="C359" s="2" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3">
+      <c r="A360" s="3" t="s">
         <v>951</v>
       </c>
-      <c r="C359" s="2" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" s="3" t="s">
+      <c r="B360" s="3" t="s">
         <v>952</v>
       </c>
-      <c r="B360" s="3" t="s">
+      <c r="C360" s="3" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3">
+      <c r="A361" s="2" t="s">
         <v>953</v>
       </c>
-      <c r="C360" s="3" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" s="2" t="s">
+      <c r="B361" s="2" t="s">
         <v>954</v>
       </c>
-      <c r="B361" s="2" t="s">
+      <c r="C361" s="2" t="s">
         <v>955</v>
       </c>
-      <c r="C361" s="2" t="s">
+    </row>
+    <row r="362" spans="1:3">
+      <c r="A362" s="3" t="s">
         <v>956</v>
       </c>
-    </row>
-    <row r="362">
-      <c r="A362" s="3" t="s">
+      <c r="B362" s="3" t="s">
         <v>957</v>
       </c>
-      <c r="B362" s="3" t="s">
+      <c r="C362" s="3" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3">
+      <c r="A363" s="2" t="s">
         <v>958</v>
       </c>
-      <c r="C362" s="3" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" s="2" t="s">
+      <c r="B363" s="2" t="s">
         <v>959</v>
       </c>
-      <c r="B363" s="2" t="s">
+      <c r="C363" s="2" t="s">
         <v>960</v>
       </c>
-      <c r="C363" s="2" t="s">
+    </row>
+    <row r="364" spans="1:3">
+      <c r="A364" s="4" t="s">
         <v>961</v>
       </c>
-    </row>
-    <row r="364">
-      <c r="A364" s="4" t="s">
+      <c r="B364" s="3" t="s">
         <v>962</v>
       </c>
-      <c r="B364" s="3" t="s">
+      <c r="C364" s="3" t="s">
         <v>963</v>
       </c>
-      <c r="C364" s="3" t="s">
+    </row>
+    <row r="365" spans="1:3">
+      <c r="A365" s="2" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="365">
-      <c r="A365" s="2" t="s">
+      <c r="B365" s="2" t="s">
         <v>965</v>
       </c>
-      <c r="B365" s="2" t="s">
+      <c r="C365" s="2" t="s">
         <v>966</v>
       </c>
-      <c r="C365" s="2" t="s">
+    </row>
+    <row r="366" spans="1:3">
+      <c r="A366" s="3" t="s">
         <v>967</v>
       </c>
-    </row>
-    <row r="366">
-      <c r="A366" s="3" t="s">
+      <c r="B366" s="3" t="s">
         <v>968</v>
       </c>
-      <c r="B366" s="3" t="s">
+      <c r="C366" s="3" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3">
+      <c r="A367" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="C366" s="3" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" s="2" t="s">
+      <c r="B367" s="2" t="s">
         <v>970</v>
       </c>
-      <c r="B367" s="2" t="s">
+      <c r="C367" s="2" t="s">
         <v>971</v>
       </c>
-      <c r="C367" s="2" t="s">
+    </row>
+    <row r="368" spans="1:3">
+      <c r="A368" s="3" t="s">
         <v>972</v>
       </c>
-    </row>
-    <row r="368">
-      <c r="A368" s="3" t="s">
+      <c r="B368" s="3" t="s">
         <v>973</v>
       </c>
-      <c r="B368" s="3" t="s">
+      <c r="C368" s="3" t="s">
         <v>974</v>
       </c>
-      <c r="C368" s="3" t="s">
+    </row>
+    <row r="369" spans="1:3">
+      <c r="A369" s="2" t="s">
         <v>975</v>
       </c>
-    </row>
-    <row r="369">
-      <c r="A369" s="2" t="s">
+      <c r="B369" s="2" t="s">
         <v>976</v>
       </c>
-      <c r="B369" s="2" t="s">
+      <c r="C369" s="2" t="s">
         <v>977</v>
       </c>
-      <c r="C369" s="2" t="s">
+    </row>
+    <row r="370" spans="1:3">
+      <c r="A370" s="3" t="s">
         <v>978</v>
       </c>
-    </row>
-    <row r="370">
-      <c r="A370" s="3" t="s">
+      <c r="B370" s="3" t="s">
         <v>979</v>
       </c>
-      <c r="B370" s="3" t="s">
+      <c r="C370" s="3" t="s">
         <v>980</v>
       </c>
-      <c r="C370" s="3" t="s">
+    </row>
+    <row r="371" spans="1:3">
+      <c r="A371" s="2" t="s">
         <v>981</v>
       </c>
-    </row>
-    <row r="371">
-      <c r="A371" s="2" t="s">
+      <c r="B371" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="B371" s="2" t="s">
+      <c r="C371" s="2" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3">
+      <c r="A372" s="3" t="s">
         <v>983</v>
       </c>
-      <c r="C371" s="2" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" s="3" t="s">
+      <c r="B372" s="3" t="s">
         <v>984</v>
       </c>
-      <c r="B372" s="3" t="s">
+      <c r="C372" s="3" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3">
+      <c r="A373" s="2" t="s">
         <v>985</v>
       </c>
-      <c r="C372" s="3" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" s="2" t="s">
+      <c r="B373" s="2" t="s">
         <v>986</v>
       </c>
-      <c r="B373" s="2" t="s">
+      <c r="C373" s="2" t="s">
         <v>987</v>
       </c>
-      <c r="C373" s="2" t="s">
+    </row>
+    <row r="374" spans="1:3">
+      <c r="A374" s="3" t="s">
         <v>988</v>
       </c>
-    </row>
-    <row r="374">
-      <c r="A374" s="3" t="s">
+      <c r="B374" s="3" t="s">
         <v>989</v>
       </c>
-      <c r="B374" s="3" t="s">
+      <c r="C374" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3">
+      <c r="A375" s="2" t="s">
         <v>990</v>
       </c>
-      <c r="C374" s="3" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" s="2" t="s">
+      <c r="B375" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="B375" s="2" t="s">
+      <c r="C375" s="2" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3">
+      <c r="A376" s="3" t="s">
         <v>992</v>
       </c>
-      <c r="C375" s="2" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" s="3" t="s">
+      <c r="B376" s="3" t="s">
         <v>993</v>
       </c>
-      <c r="B376" s="3" t="s">
+      <c r="C376" s="3" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3">
+      <c r="A377" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="C376" s="3" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" s="2" t="s">
+      <c r="B377" s="2" t="s">
         <v>995</v>
       </c>
-      <c r="B377" s="2" t="s">
+      <c r="C377" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3">
+      <c r="A378" s="3" t="s">
         <v>996</v>
       </c>
-      <c r="C377" s="2" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" s="3" t="s">
+      <c r="B378" s="3" t="s">
         <v>997</v>
       </c>
-      <c r="B378" s="3" t="s">
+      <c r="C378" s="3" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3">
+      <c r="A379" s="2" t="s">
         <v>998</v>
       </c>
-      <c r="C378" s="3" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" s="2" t="s">
+      <c r="B379" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="B379" s="2" t="s">
+      <c r="C379" s="2" t="s">
         <v>1000</v>
       </c>
-      <c r="C379" s="2" t="s">
+    </row>
+    <row r="380" spans="1:3">
+      <c r="A380" s="3" t="s">
         <v>1001</v>
       </c>
-    </row>
-    <row r="380">
-      <c r="A380" s="3" t="s">
+      <c r="B380" s="3" t="s">
         <v>1002</v>
       </c>
-      <c r="B380" s="3" t="s">
+      <c r="C380" s="3" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3">
+      <c r="A381" s="2" t="s">
         <v>1003</v>
       </c>
-      <c r="C380" s="3" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" s="2" t="s">
+      <c r="B381" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="B381" s="2" t="s">
+      <c r="C381" s="2" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3">
+      <c r="A382" s="3" t="s">
         <v>1005</v>
       </c>
-      <c r="C381" s="2" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" s="3" t="s">
+      <c r="B382" s="3" t="s">
         <v>1006</v>
       </c>
-      <c r="B382" s="3" t="s">
+      <c r="C382" s="3" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3">
+      <c r="A383" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="C382" s="3" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" s="2" t="s">
+      <c r="B383" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="B383" s="2" t="s">
+      <c r="C383" s="2" t="s">
         <v>1009</v>
       </c>
-      <c r="C383" s="2" t="s">
+    </row>
+    <row r="384" spans="1:3">
+      <c r="A384" s="3" t="s">
         <v>1010</v>
       </c>
-    </row>
-    <row r="384">
-      <c r="A384" s="3" t="s">
+      <c r="B384" s="3" t="s">
         <v>1011</v>
       </c>
-      <c r="B384" s="3" t="s">
+      <c r="C384" s="3" t="s">
         <v>1012</v>
       </c>
-      <c r="C384" s="3" t="s">
+    </row>
+    <row r="385" spans="1:3">
+      <c r="A385" s="2" t="s">
         <v>1013</v>
       </c>
-    </row>
-    <row r="385">
-      <c r="A385" s="2" t="s">
+      <c r="B385" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="B385" s="2" t="s">
+      <c r="C385" s="2" t="s">
         <v>1015</v>
       </c>
-      <c r="C385" s="2" t="s">
+    </row>
+    <row r="386" spans="1:3">
+      <c r="A386" s="3" t="s">
         <v>1016</v>
       </c>
-    </row>
-    <row r="386">
-      <c r="A386" s="3" t="s">
+      <c r="B386" s="3" t="s">
         <v>1017</v>
       </c>
-      <c r="B386" s="3" t="s">
+      <c r="C386" s="3" t="s">
         <v>1018</v>
       </c>
-      <c r="C386" s="3" t="s">
+    </row>
+    <row r="387" spans="1:3">
+      <c r="A387" s="2" t="s">
         <v>1019</v>
       </c>
-    </row>
-    <row r="387">
-      <c r="A387" s="2" t="s">
+      <c r="B387" s="2" t="s">
         <v>1020</v>
       </c>
-      <c r="B387" s="2" t="s">
+      <c r="C387" s="2" t="s">
         <v>1021</v>
       </c>
-      <c r="C387" s="2" t="s">
+    </row>
+    <row r="388" spans="1:3">
+      <c r="A388" s="3" t="s">
         <v>1022</v>
       </c>
-    </row>
-    <row r="388">
-      <c r="A388" s="3" t="s">
+      <c r="B388" s="3" t="s">
         <v>1023</v>
       </c>
-      <c r="B388" s="3" t="s">
+      <c r="C388" s="3" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3">
+      <c r="A389" s="2" t="s">
         <v>1024</v>
       </c>
-      <c r="C388" s="3" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" s="2" t="s">
+      <c r="B389" s="2" t="s">
         <v>1025</v>
       </c>
-      <c r="B389" s="2" t="s">
+      <c r="C389" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="C389" s="2" t="s">
+    </row>
+    <row r="390" spans="1:3">
+      <c r="A390" s="3" t="s">
         <v>1027</v>
       </c>
-    </row>
-    <row r="390">
-      <c r="A390" s="3" t="s">
+      <c r="B390" s="3" t="s">
         <v>1028</v>
       </c>
-      <c r="B390" s="3" t="s">
+      <c r="C390" s="3" t="s">
         <v>1029</v>
       </c>
-      <c r="C390" s="3" t="s">
+    </row>
+    <row r="391" spans="1:3">
+      <c r="A391" s="2" t="s">
         <v>1030</v>
       </c>
-    </row>
-    <row r="391">
-      <c r="A391" s="2" t="s">
+      <c r="B391" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="B391" s="2" t="s">
+      <c r="C391" s="2" t="s">
         <v>1032</v>
       </c>
-      <c r="C391" s="2" t="s">
+    </row>
+    <row r="392" spans="1:3">
+      <c r="A392" s="3" t="s">
         <v>1033</v>
       </c>
-    </row>
-    <row r="392">
-      <c r="A392" s="3" t="s">
+      <c r="B392" s="3" t="s">
         <v>1034</v>
       </c>
-      <c r="B392" s="3" t="s">
+      <c r="C392" s="3" t="s">
         <v>1035</v>
       </c>
-      <c r="C392" s="3" t="s">
+    </row>
+    <row r="393" spans="1:3">
+      <c r="A393" s="2" t="s">
         <v>1036</v>
       </c>
-    </row>
-    <row r="393">
-      <c r="A393" s="2" t="s">
+      <c r="B393" s="2" t="s">
         <v>1037</v>
       </c>
-      <c r="B393" s="2" t="s">
+      <c r="C393" s="2" t="s">
         <v>1038</v>
       </c>
-      <c r="C393" s="2" t="s">
+    </row>
+    <row r="394" spans="1:3">
+      <c r="A394" s="3" t="s">
         <v>1039</v>
       </c>
-    </row>
-    <row r="394">
-      <c r="A394" s="3" t="s">
+      <c r="B394" s="3" t="s">
         <v>1040</v>
       </c>
-      <c r="B394" s="3" t="s">
+      <c r="C394" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="C394" s="3" t="s">
+    </row>
+    <row r="395" spans="1:3">
+      <c r="A395" s="2" t="s">
         <v>1042</v>
       </c>
-    </row>
-    <row r="395">
-      <c r="A395" s="2" t="s">
+      <c r="B395" s="2" t="s">
         <v>1043</v>
       </c>
-      <c r="B395" s="2" t="s">
+      <c r="C395" s="2" t="s">
         <v>1044</v>
       </c>
-      <c r="C395" s="2" t="s">
+    </row>
+    <row r="396" spans="1:3">
+      <c r="A396" s="3" t="s">
         <v>1045</v>
       </c>
-    </row>
-    <row r="396">
-      <c r="A396" s="3" t="s">
+      <c r="B396" s="3" t="s">
         <v>1046</v>
       </c>
-      <c r="B396" s="3" t="s">
+      <c r="C396" s="3" t="s">
         <v>1047</v>
       </c>
-      <c r="C396" s="3" t="s">
+    </row>
+    <row r="397" spans="1:3">
+      <c r="A397" s="3" t="s">
         <v>1048</v>
       </c>
-    </row>
-    <row r="397">
-      <c r="A397" s="3" t="s">
+      <c r="B397" s="3" t="s">
         <v>1049</v>
       </c>
-      <c r="B397" s="3" t="s">
+      <c r="C397" s="3" t="s">
         <v>1050</v>
       </c>
-      <c r="C397" s="3" t="s">
+    </row>
+    <row r="398" spans="1:3">
+      <c r="A398" s="2" t="s">
         <v>1051</v>
       </c>
-    </row>
-    <row r="398">
-      <c r="A398" s="2" t="s">
+      <c r="B398" s="2" t="s">
         <v>1052</v>
       </c>
-      <c r="B398" s="2" t="s">
+      <c r="C398" s="5"/>
+    </row>
+    <row r="399" spans="1:3">
+      <c r="A399" s="3" t="s">
         <v>1053</v>
       </c>
-      <c r="C398" s="5"/>
-    </row>
-    <row r="399">
-      <c r="A399" s="3" t="s">
+      <c r="B399" s="3" t="s">
         <v>1054</v>
       </c>
-      <c r="B399" s="3" t="s">
+      <c r="C399" s="6"/>
+    </row>
+    <row r="400" spans="1:3">
+      <c r="A400" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C399" s="6"/>
-    </row>
-    <row r="400">
-      <c r="A400" s="2" t="s">
+      <c r="B400" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="B400" s="2" t="s">
+      <c r="C400" s="5"/>
+    </row>
+    <row r="401" spans="1:3">
+      <c r="A401" s="3" t="s">
         <v>1057</v>
       </c>
-      <c r="C400" s="5"/>
-    </row>
-    <row r="401">
-      <c r="A401" s="3" t="s">
+      <c r="B401" s="3" t="s">
         <v>1058</v>
       </c>
-      <c r="B401" s="3" t="s">
+      <c r="C401" s="6"/>
+    </row>
+    <row r="402" spans="1:3">
+      <c r="A402" s="2" t="s">
         <v>1059</v>
       </c>
-      <c r="C401" s="6"/>
-    </row>
-    <row r="402">
-      <c r="A402" s="2" t="s">
+      <c r="B402" s="2" t="s">
         <v>1060</v>
       </c>
-      <c r="B402" s="2" t="s">
+      <c r="C402" s="5"/>
+    </row>
+    <row r="403" spans="1:3">
+      <c r="A403" s="3" t="s">
         <v>1061</v>
       </c>
-      <c r="C402" s="5"/>
-    </row>
-    <row r="403">
-      <c r="A403" s="3" t="s">
+      <c r="B403" s="3" t="s">
         <v>1062</v>
       </c>
-      <c r="B403" s="3" t="s">
+      <c r="C403" s="6"/>
+    </row>
+    <row r="404" spans="1:3">
+      <c r="A404" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="C403" s="6"/>
-    </row>
-    <row r="404">
-      <c r="A404" s="2" t="s">
+      <c r="B404" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="B404" s="2" t="s">
+      <c r="C404" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="C404" s="2" t="s">
+    </row>
+    <row r="405" spans="1:3">
+      <c r="A405" s="3" t="s">
         <v>1066</v>
       </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="3" t="s">
+      <c r="B405" s="3" t="s">
         <v>1067</v>
       </c>
-      <c r="B405" s="3" t="s">
+      <c r="C405" s="6"/>
+    </row>
+    <row r="406" spans="1:3">
+      <c r="A406" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="C405" s="6"/>
-    </row>
-    <row r="406">
-      <c r="A406" s="2" t="s">
+      <c r="B406" s="2" t="s">
         <v>1069</v>
       </c>
-      <c r="B406" s="2" t="s">
+      <c r="C406" s="2" t="s">
         <v>1070</v>
       </c>
-      <c r="C406" s="2" t="s">
+    </row>
+    <row r="407" spans="1:3">
+      <c r="A407" s="3" t="s">
         <v>1071</v>
       </c>
-    </row>
-    <row r="407">
-      <c r="A407" s="3" t="s">
+      <c r="B407" s="3" t="s">
         <v>1072</v>
       </c>
-      <c r="B407" s="3" t="s">
+      <c r="C407" s="6"/>
+    </row>
+    <row r="408" spans="1:3">
+      <c r="A408" s="2" t="s">
         <v>1073</v>
       </c>
-      <c r="C407" s="6"/>
-    </row>
-    <row r="408">
-      <c r="A408" s="2" t="s">
+      <c r="B408" s="2" t="s">
         <v>1074</v>
       </c>
-      <c r="B408" s="2" t="s">
+      <c r="C408" s="2" t="s">
         <v>1075</v>
       </c>
-      <c r="C408" s="2" t="s">
+    </row>
+    <row r="409" spans="1:3">
+      <c r="A409" s="3" t="s">
         <v>1076</v>
       </c>
-    </row>
-    <row r="409">
-      <c r="A409" s="3" t="s">
+      <c r="B409" s="3" t="s">
         <v>1077</v>
       </c>
-      <c r="B409" s="3" t="s">
+      <c r="C409" s="3" t="s">
         <v>1078</v>
       </c>
-      <c r="C409" s="3" t="s">
+    </row>
+    <row r="410" spans="1:3">
+      <c r="A410" s="2" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="410">
-      <c r="A410" s="2" t="s">
+      <c r="B410" s="2" t="s">
         <v>1080</v>
       </c>
-      <c r="B410" s="2" t="s">
+      <c r="C410" s="2" t="s">
         <v>1081</v>
       </c>
-      <c r="C410" s="2" t="s">
+    </row>
+    <row r="411" spans="1:3">
+      <c r="A411" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="411">
-      <c r="A411" s="3" t="s">
+      <c r="B411" s="3" t="s">
         <v>1083</v>
       </c>
-      <c r="B411" s="3" t="s">
+      <c r="C411" s="3" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3">
+      <c r="A412" s="2" t="s">
         <v>1084</v>
       </c>
-      <c r="C411" s="3" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" s="2" t="s">
+      <c r="B412" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="B412" s="2" t="s">
+      <c r="C412" s="5"/>
+    </row>
+    <row r="413" spans="1:3">
+      <c r="A413" s="3" t="s">
         <v>1086</v>
       </c>
-      <c r="C412" s="5"/>
-    </row>
-    <row r="413">
-      <c r="A413" s="3" t="s">
+      <c r="B413" s="3" t="s">
         <v>1087</v>
       </c>
-      <c r="B413" s="3" t="s">
+      <c r="C413" s="3" t="s">
         <v>1088</v>
       </c>
-      <c r="C413" s="3" t="s">
+    </row>
+    <row r="414" spans="1:3">
+      <c r="A414" s="2" t="s">
         <v>1089</v>
       </c>
-    </row>
-    <row r="414">
-      <c r="A414" s="2" t="s">
+      <c r="B414" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="B414" s="2" t="s">
+      <c r="C414" s="5"/>
+    </row>
+    <row r="415" spans="1:3">
+      <c r="A415" s="3" t="s">
         <v>1091</v>
       </c>
-      <c r="C414" s="5"/>
-    </row>
-    <row r="415">
-      <c r="A415" s="3" t="s">
+      <c r="B415" s="3" t="s">
         <v>1092</v>
       </c>
-      <c r="B415" s="3" t="s">
+      <c r="C415" s="3" t="s">
         <v>1093</v>
       </c>
-      <c r="C415" s="3" t="s">
+    </row>
+    <row r="416" spans="1:3">
+      <c r="A416" s="2" t="s">
         <v>1094</v>
       </c>
-    </row>
-    <row r="416">
-      <c r="A416" s="2" t="s">
+      <c r="B416" s="2" t="s">
         <v>1095</v>
       </c>
-      <c r="B416" s="2" t="s">
+      <c r="C416" s="5"/>
+    </row>
+    <row r="417" spans="1:3">
+      <c r="A417" s="3" t="s">
         <v>1096</v>
       </c>
-      <c r="C416" s="5"/>
-    </row>
-    <row r="417">
-      <c r="A417" s="3" t="s">
+      <c r="B417" s="3" t="s">
         <v>1097</v>
       </c>
-      <c r="B417" s="3" t="s">
+      <c r="C417" s="3" t="s">
         <v>1098</v>
       </c>
-      <c r="C417" s="3" t="s">
+    </row>
+    <row r="418" spans="1:3">
+      <c r="A418" s="2" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="418">
-      <c r="A418" s="2" t="s">
+      <c r="B418" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="B418" s="2" t="s">
+      <c r="C418" s="2" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3">
+      <c r="A419" s="3" t="s">
         <v>1101</v>
       </c>
-      <c r="C418" s="2" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" s="3" t="s">
+      <c r="B419" s="3" t="s">
         <v>1102</v>
       </c>
-      <c r="B419" s="3" t="s">
+      <c r="C419" s="6"/>
+    </row>
+    <row r="420" spans="1:3">
+      <c r="A420" s="2" t="s">
         <v>1103</v>
       </c>
-      <c r="C419" s="6"/>
-    </row>
-    <row r="420">
-      <c r="A420" s="2" t="s">
+      <c r="B420" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="B420" s="2" t="s">
+      <c r="C420" s="5"/>
+    </row>
+    <row r="421" spans="1:3">
+      <c r="A421" s="3" t="s">
         <v>1105</v>
       </c>
-      <c r="C420" s="5"/>
-    </row>
-    <row r="421">
-      <c r="A421" s="3" t="s">
+      <c r="B421" s="3" t="s">
         <v>1106</v>
       </c>
-      <c r="B421" s="3" t="s">
+      <c r="C421" s="6"/>
+    </row>
+    <row r="422" spans="1:3">
+      <c r="A422" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="C421" s="6"/>
-    </row>
-    <row r="422">
-      <c r="A422" s="2" t="s">
+      <c r="B422" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="B422" s="2" t="s">
+      <c r="C422" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="C422" s="2" t="s">
+    </row>
+    <row r="423" spans="1:3">
+      <c r="A423" s="3" t="s">
         <v>1110</v>
       </c>
-    </row>
-    <row r="423">
-      <c r="A423" s="3" t="s">
+      <c r="B423" s="3" t="s">
         <v>1111</v>
       </c>
-      <c r="B423" s="3" t="s">
+      <c r="C423" s="3" t="s">
         <v>1112</v>
       </c>
-      <c r="C423" s="3" t="s">
+    </row>
+    <row r="424" spans="1:3">
+      <c r="A424" s="2" t="s">
         <v>1113</v>
       </c>
-    </row>
-    <row r="424">
-      <c r="A424" s="2" t="s">
+      <c r="B424" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B424" s="2" t="s">
+      <c r="C424" s="2" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3">
+      <c r="A425" s="3" t="s">
         <v>1115</v>
       </c>
-      <c r="C424" s="2" t="s">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" s="3" t="s">
+      <c r="B425" s="3" t="s">
         <v>1116</v>
       </c>
-      <c r="B425" s="3" t="s">
+      <c r="C425" s="3" t="s">
         <v>1117</v>
       </c>
-      <c r="C425" s="3" t="s">
+    </row>
+    <row r="426" spans="1:3">
+      <c r="A426" s="2" t="s">
         <v>1118</v>
       </c>
-    </row>
-    <row r="426">
-      <c r="A426" s="2" t="s">
+      <c r="B426" s="2" t="s">
         <v>1119</v>
       </c>
-      <c r="B426" s="2" t="s">
+      <c r="C426" s="2" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3">
+      <c r="A427" s="3" t="s">
         <v>1120</v>
       </c>
-      <c r="C426" s="2" t="s">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" s="3" t="s">
+      <c r="B427" s="3" t="s">
         <v>1121</v>
       </c>
-      <c r="B427" s="3" t="s">
+      <c r="C427" s="3" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3">
+      <c r="A428" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="C427" s="3" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" s="2" t="s">
+      <c r="B428" s="2" t="s">
         <v>1123</v>
       </c>
-      <c r="B428" s="2" t="s">
+      <c r="C428" s="2" t="s">
         <v>1124</v>
       </c>
-      <c r="C428" s="2" t="s">
+    </row>
+    <row r="429" spans="1:3">
+      <c r="A429" s="3" t="s">
         <v>1125</v>
       </c>
-    </row>
-    <row r="429">
-      <c r="A429" s="3" t="s">
+      <c r="B429" s="3" t="s">
         <v>1126</v>
       </c>
-      <c r="B429" s="3" t="s">
+      <c r="C429" s="3" t="s">
         <v>1127</v>
       </c>
-      <c r="C429" s="3" t="s">
+    </row>
+    <row r="430" spans="1:3">
+      <c r="A430" s="2" t="s">
         <v>1128</v>
       </c>
-    </row>
-    <row r="430">
-      <c r="A430" s="2" t="s">
+      <c r="B430" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="B430" s="2" t="s">
+      <c r="C430" s="5"/>
+    </row>
+    <row r="431" spans="1:3">
+      <c r="A431" s="3" t="s">
         <v>1130</v>
       </c>
-      <c r="C430" s="5"/>
-    </row>
-    <row r="431">
-      <c r="A431" s="3" t="s">
+      <c r="B431" s="3" t="s">
         <v>1131</v>
       </c>
-      <c r="B431" s="3" t="s">
+      <c r="C431" s="3" t="s">
         <v>1132</v>
       </c>
-      <c r="C431" s="3" t="s">
+    </row>
+    <row r="432" spans="1:3">
+      <c r="A432" s="3" t="s">
         <v>1133</v>
       </c>
-    </row>
-    <row r="432">
-      <c r="A432" s="3" t="s">
+      <c r="B432" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="C432" s="3" t="s">
         <v>1134</v>
       </c>
-      <c r="B432" s="3" t="s">
-        <v>912</v>
-      </c>
-      <c r="C432" s="3" t="s">
+    </row>
+    <row r="433" spans="1:3">
+      <c r="A433" s="2" t="s">
         <v>1135</v>
       </c>
-    </row>
-    <row r="433">
-      <c r="A433" s="2" t="s">
+      <c r="B433" s="2" t="s">
         <v>1136</v>
       </c>
-      <c r="B433" s="2" t="s">
+      <c r="C433" s="2" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3">
+      <c r="A434" s="3" t="s">
         <v>1137</v>
       </c>
-      <c r="C433" s="2" t="s">
-        <v>1137</v>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" s="3" t="s">
+      <c r="B434" s="3" t="s">
         <v>1138</v>
       </c>
-      <c r="B434" s="3" t="s">
+      <c r="C434" s="3" t="s">
         <v>1139</v>
       </c>
-      <c r="C434" s="3" t="s">
+    </row>
+    <row r="435" spans="1:3">
+      <c r="A435" s="2" t="s">
         <v>1140</v>
       </c>
-    </row>
-    <row r="435">
-      <c r="A435" s="2" t="s">
+      <c r="B435" s="2" t="s">
         <v>1141</v>
       </c>
-      <c r="B435" s="2" t="s">
+      <c r="C435" s="2" t="s">
         <v>1142</v>
       </c>
-      <c r="C435" s="2" t="s">
+    </row>
+    <row r="436" spans="1:3">
+      <c r="A436" s="7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B436" s="2" t="s">
         <v>1143</v>
       </c>
-    </row>
-    <row r="436">
-      <c r="A436" s="7" t="s">
-        <v>1054</v>
-      </c>
-      <c r="B436" s="2" t="s">
+      <c r="C436" s="5"/>
+    </row>
+    <row r="437" spans="1:3">
+      <c r="A437" s="8" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B437" s="3" t="s">
         <v>1144</v>
       </c>
-      <c r="C436" s="5"/>
-    </row>
-    <row r="437">
-      <c r="A437" s="8" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B437" s="3" t="s">
+      <c r="C437" s="6"/>
+    </row>
+    <row r="438" spans="1:3">
+      <c r="A438" s="7" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B438" s="2" t="s">
         <v>1145</v>
       </c>
-      <c r="C437" s="6"/>
-    </row>
-    <row r="438">
-      <c r="A438" s="7" t="s">
-        <v>1060</v>
-      </c>
-      <c r="B438" s="2" t="s">
+      <c r="C438" s="5"/>
+    </row>
+    <row r="439" spans="1:3">
+      <c r="A439" s="8" t="s">
         <v>1146</v>
       </c>
-      <c r="C438" s="5"/>
-    </row>
-    <row r="439">
-      <c r="A439" s="8" t="s">
+      <c r="B439" s="8" t="s">
         <v>1147</v>
       </c>
-      <c r="B439" s="8" t="s">
+      <c r="C439" s="3" t="s">
         <v>1148</v>
       </c>
-      <c r="C439" s="3" t="s">
+    </row>
+    <row r="440" spans="1:3">
+      <c r="A440" s="8" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B440" s="8" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C440" s="6"/>
+    </row>
+    <row r="441" spans="1:3">
+      <c r="A441" s="2" t="s">
         <v>1149</v>
       </c>
-    </row>
-    <row r="440">
-      <c r="A440" s="8" t="s">
-        <v>1056</v>
-      </c>
-      <c r="B440" s="8" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C440" s="6"/>
-    </row>
-    <row r="441">
-      <c r="A441" s="2" t="s">
+      <c r="B441" s="2" t="s">
         <v>1150</v>
       </c>
-      <c r="B441" s="2" t="s">
+      <c r="C441" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="C441" s="2" t="s">
+    </row>
+    <row r="442" spans="1:3">
+      <c r="A442" s="2" t="s">
         <v>1152</v>
       </c>
-    </row>
-    <row r="442">
-      <c r="A442" s="2" t="s">
+      <c r="B442" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="B442" s="2" t="s">
+      <c r="C442" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="C442" s="2" t="s">
+    </row>
+    <row r="443" spans="1:3">
+      <c r="A443" s="3" t="s">
         <v>1155</v>
       </c>
-    </row>
-    <row r="443">
-      <c r="A443" s="3" t="s">
+      <c r="B443" s="3" t="s">
         <v>1156</v>
       </c>
-      <c r="B443" s="3" t="s">
+      <c r="C443" s="3" t="s">
         <v>1157</v>
       </c>
-      <c r="C443" s="3" t="s">
+    </row>
+    <row r="444" spans="1:3">
+      <c r="A444" s="2" t="s">
         <v>1158</v>
       </c>
-    </row>
-    <row r="444">
-      <c r="A444" s="2" t="s">
+      <c r="B444" s="2" t="s">
         <v>1159</v>
       </c>
-      <c r="B444" s="2" t="s">
+      <c r="C444" s="2" t="s">
         <v>1160</v>
       </c>
-      <c r="C444" s="2" t="s">
+    </row>
+    <row r="445" spans="1:3">
+      <c r="A445" s="3" t="s">
         <v>1161</v>
       </c>
-    </row>
-    <row r="445">
-      <c r="A445" s="3" t="s">
+      <c r="B445" s="3" t="s">
         <v>1162</v>
       </c>
-      <c r="B445" s="3" t="s">
+      <c r="C445" s="3" t="s">
         <v>1163</v>
       </c>
-      <c r="C445" s="3" t="s">
+    </row>
+    <row r="446" spans="1:3">
+      <c r="A446" s="2" t="s">
         <v>1164</v>
       </c>
-    </row>
-    <row r="446">
-      <c r="A446" s="2" t="s">
+      <c r="B446" s="2" t="s">
         <v>1165</v>
       </c>
-      <c r="B446" s="2" t="s">
+      <c r="C446" s="2" t="s">
         <v>1166</v>
       </c>
-      <c r="C446" s="2" t="s">
+    </row>
+    <row r="447" spans="1:3">
+      <c r="A447" s="3" t="s">
         <v>1167</v>
       </c>
-    </row>
-    <row r="447">
-      <c r="A447" s="3" t="s">
+      <c r="B447" s="3" t="s">
         <v>1168</v>
       </c>
-      <c r="B447" s="3" t="s">
+      <c r="C447" s="3" t="s">
         <v>1169</v>
       </c>
-      <c r="C447" s="3" t="s">
+    </row>
+    <row r="448" spans="1:3">
+      <c r="A448" s="2" t="s">
         <v>1170</v>
       </c>
-    </row>
-    <row r="448">
-      <c r="A448" s="2" t="s">
+      <c r="B448" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="B448" s="2" t="s">
+      <c r="C448" s="2" t="s">
         <v>1172</v>
       </c>
-      <c r="C448" s="2" t="s">
+    </row>
+    <row r="449" spans="1:3">
+      <c r="A449" s="3" t="s">
         <v>1173</v>
       </c>
-    </row>
-    <row r="449">
-      <c r="A449" s="3" t="s">
+      <c r="B449" s="3" t="s">
         <v>1174</v>
       </c>
-      <c r="B449" s="3" t="s">
+      <c r="C449" s="3" t="s">
         <v>1175</v>
       </c>
-      <c r="C449" s="3" t="s">
+    </row>
+    <row r="450" spans="1:3">
+      <c r="A450" s="2" t="s">
         <v>1176</v>
       </c>
-    </row>
-    <row r="450">
-      <c r="A450" s="2" t="s">
+      <c r="B450" s="2" t="s">
         <v>1177</v>
       </c>
-      <c r="B450" s="2" t="s">
+      <c r="C450" s="2" t="s">
         <v>1178</v>
       </c>
-      <c r="C450" s="2" t="s">
+    </row>
+    <row r="451" spans="1:3">
+      <c r="A451" s="3" t="s">
         <v>1179</v>
       </c>
-    </row>
-    <row r="451">
-      <c r="A451" s="3" t="s">
+      <c r="B451" s="3" t="s">
         <v>1180</v>
       </c>
-      <c r="B451" s="3" t="s">
+      <c r="C451" s="3" t="s">
         <v>1181</v>
       </c>
-      <c r="C451" s="3" t="s">
+    </row>
+    <row r="452" spans="1:3">
+      <c r="A452" s="2" t="s">
         <v>1182</v>
       </c>
-    </row>
-    <row r="452">
-      <c r="A452" s="2" t="s">
+      <c r="B452" s="2" t="s">
         <v>1183</v>
       </c>
-      <c r="B452" s="2" t="s">
+      <c r="C452" s="2" t="s">
         <v>1184</v>
       </c>
-      <c r="C452" s="2" t="s">
+    </row>
+    <row r="453" spans="1:3">
+      <c r="A453" s="3" t="s">
         <v>1185</v>
       </c>
-    </row>
-    <row r="453">
-      <c r="A453" s="3" t="s">
+      <c r="B453" s="3" t="s">
         <v>1186</v>
       </c>
-      <c r="B453" s="3" t="s">
+      <c r="C453" s="3" t="s">
         <v>1187</v>
       </c>
-      <c r="C453" s="3" t="s">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" s="9"/>
-      <c r="B454" s="9"/>
+    </row>
+    <row r="454" spans="1:3">
       <c r="C454" s="9"/>
     </row>
-    <row r="455">
-      <c r="A455" s="9"/>
-      <c r="B455" s="9"/>
+    <row r="455" spans="1:3">
       <c r="C455" s="9"/>
     </row>
-    <row r="456">
-      <c r="A456" s="9"/>
-      <c r="B456" s="9"/>
+    <row r="456" spans="1:3">
       <c r="C456" s="9"/>
     </row>
-    <row r="457">
-      <c r="A457" s="9"/>
-      <c r="B457" s="9"/>
+    <row r="457" spans="1:3">
       <c r="C457" s="9"/>
     </row>
-    <row r="458">
-      <c r="A458" s="9"/>
-      <c r="B458" s="9"/>
+    <row r="458" spans="1:3">
       <c r="C458" s="9"/>
     </row>
-    <row r="459">
-      <c r="A459" s="9"/>
-      <c r="B459" s="9"/>
+    <row r="459" spans="1:3">
       <c r="C459" s="9"/>
     </row>
-    <row r="460">
-      <c r="A460" s="9"/>
-      <c r="B460" s="9"/>
+    <row r="460" spans="1:3">
       <c r="C460" s="9"/>
     </row>
-    <row r="461">
-      <c r="A461" s="9"/>
-      <c r="B461" s="9"/>
+    <row r="461" spans="1:3">
       <c r="C461" s="9"/>
     </row>
-    <row r="462">
-      <c r="A462" s="9"/>
-      <c r="B462" s="9"/>
+    <row r="462" spans="1:3">
       <c r="C462" s="9"/>
     </row>
-    <row r="463">
-      <c r="A463" s="9"/>
-      <c r="B463" s="9"/>
+    <row r="463" spans="1:3">
       <c r="C463" s="9"/>
     </row>
-    <row r="464">
-      <c r="A464" s="9"/>
-      <c r="B464" s="9"/>
+    <row r="464" spans="1:3">
       <c r="C464" s="9"/>
     </row>
-    <row r="465">
-      <c r="A465" s="9"/>
-      <c r="B465" s="9"/>
+    <row r="465" spans="3:3">
       <c r="C465" s="9"/>
     </row>
-    <row r="466">
-      <c r="A466" s="9"/>
-      <c r="B466" s="9"/>
+    <row r="466" spans="3:3">
       <c r="C466" s="9"/>
     </row>
-    <row r="467">
-      <c r="A467" s="9"/>
-      <c r="B467" s="9"/>
+    <row r="467" spans="3:3">
       <c r="C467" s="9"/>
     </row>
-    <row r="468">
-      <c r="A468" s="9"/>
-      <c r="B468" s="9"/>
+    <row r="468" spans="3:3">
       <c r="C468" s="9"/>
     </row>
-    <row r="469">
-      <c r="A469" s="9"/>
-      <c r="B469" s="9"/>
+    <row r="469" spans="3:3">
       <c r="C469" s="9"/>
     </row>
-    <row r="470">
-      <c r="A470" s="9"/>
-      <c r="B470" s="9"/>
+    <row r="470" spans="3:3">
       <c r="C470" s="9"/>
     </row>
-    <row r="471">
-      <c r="A471" s="9"/>
-      <c r="B471" s="9"/>
+    <row r="471" spans="3:3">
       <c r="C471" s="9"/>
     </row>
-    <row r="472">
-      <c r="A472" s="9"/>
-      <c r="B472" s="9"/>
+    <row r="472" spans="3:3">
       <c r="C472" s="9"/>
     </row>
-    <row r="473">
-      <c r="A473" s="9"/>
-      <c r="B473" s="9"/>
+    <row r="473" spans="3:3">
       <c r="C473" s="9"/>
     </row>
-    <row r="474">
-      <c r="A474" s="9"/>
-      <c r="B474" s="9"/>
+    <row r="474" spans="3:3">
       <c r="C474" s="9"/>
     </row>
-    <row r="475">
-      <c r="A475" s="9"/>
-      <c r="B475" s="9"/>
+    <row r="475" spans="3:3">
       <c r="C475" s="9"/>
     </row>
-    <row r="476">
-      <c r="A476" s="9"/>
-      <c r="B476" s="9"/>
+    <row r="476" spans="3:3">
       <c r="C476" s="9"/>
     </row>
-    <row r="477">
-      <c r="A477" s="9"/>
-      <c r="B477" s="9"/>
+    <row r="477" spans="3:3">
       <c r="C477" s="9"/>
     </row>
-    <row r="478">
-      <c r="A478" s="9"/>
-      <c r="B478" s="9"/>
+    <row r="478" spans="3:3">
       <c r="C478" s="9"/>
     </row>
-    <row r="479">
-      <c r="A479" s="9"/>
-      <c r="B479" s="9"/>
+    <row r="479" spans="3:3">
       <c r="C479" s="9"/>
     </row>
-    <row r="480">
-      <c r="A480" s="9"/>
-      <c r="B480" s="9"/>
+    <row r="480" spans="3:3">
       <c r="C480" s="9"/>
     </row>
-    <row r="481">
-      <c r="A481" s="9"/>
-      <c r="B481" s="9"/>
+    <row r="481" spans="3:3">
       <c r="C481" s="9"/>
     </row>
-    <row r="482">
-      <c r="A482" s="9"/>
-      <c r="B482" s="9"/>
+    <row r="482" spans="3:3">
       <c r="C482" s="9"/>
     </row>
-    <row r="483">
-      <c r="A483" s="9"/>
-      <c r="B483" s="9"/>
+    <row r="483" spans="3:3">
       <c r="C483" s="9"/>
     </row>
-    <row r="484">
-      <c r="A484" s="9"/>
-      <c r="B484" s="9"/>
+    <row r="484" spans="3:3">
       <c r="C484" s="9"/>
     </row>
-    <row r="485">
-      <c r="A485" s="9"/>
-      <c r="B485" s="9"/>
+    <row r="485" spans="3:3">
       <c r="C485" s="9"/>
     </row>
-    <row r="486">
-      <c r="A486" s="9"/>
-      <c r="B486" s="9"/>
+    <row r="486" spans="3:3">
       <c r="C486" s="9"/>
     </row>
-    <row r="487">
-      <c r="A487" s="9"/>
-      <c r="B487" s="9"/>
+    <row r="487" spans="3:3">
       <c r="C487" s="9"/>
     </row>
-    <row r="488">
-      <c r="A488" s="9"/>
-      <c r="B488" s="9"/>
+    <row r="488" spans="3:3">
       <c r="C488" s="9"/>
     </row>
-    <row r="489">
-      <c r="A489" s="9"/>
-      <c r="B489" s="9"/>
+    <row r="489" spans="3:3">
       <c r="C489" s="9"/>
     </row>
-    <row r="490">
-      <c r="A490" s="9"/>
-      <c r="B490" s="9"/>
+    <row r="490" spans="3:3">
       <c r="C490" s="9"/>
     </row>
-    <row r="491">
-      <c r="A491" s="9"/>
-      <c r="B491" s="9"/>
+    <row r="491" spans="3:3">
       <c r="C491" s="9"/>
     </row>
-    <row r="492">
-      <c r="A492" s="9"/>
-      <c r="B492" s="9"/>
+    <row r="492" spans="3:3">
       <c r="C492" s="9"/>
     </row>
-    <row r="493">
-      <c r="A493" s="9"/>
-      <c r="B493" s="9"/>
+    <row r="493" spans="3:3">
       <c r="C493" s="9"/>
     </row>
-    <row r="494">
-      <c r="A494" s="9"/>
-      <c r="B494" s="9"/>
+    <row r="494" spans="3:3">
       <c r="C494" s="9"/>
     </row>
-    <row r="495">
-      <c r="A495" s="9"/>
-      <c r="B495" s="9"/>
+    <row r="495" spans="3:3">
       <c r="C495" s="9"/>
     </row>
-    <row r="496">
-      <c r="A496" s="9"/>
-      <c r="B496" s="9"/>
+    <row r="496" spans="3:3">
       <c r="C496" s="9"/>
     </row>
-    <row r="497">
-      <c r="A497" s="9"/>
-      <c r="B497" s="9"/>
+    <row r="497" spans="3:3">
       <c r="C497" s="9"/>
     </row>
-    <row r="498">
-      <c r="A498" s="9"/>
-      <c r="B498" s="9"/>
+    <row r="498" spans="3:3">
       <c r="C498" s="9"/>
     </row>
-    <row r="499">
-      <c r="A499" s="9"/>
-      <c r="B499" s="9"/>
+    <row r="499" spans="3:3">
       <c r="C499" s="9"/>
     </row>
-    <row r="500">
-      <c r="A500" s="9"/>
-      <c r="B500" s="9"/>
+    <row r="500" spans="3:3">
       <c r="C500" s="9"/>
     </row>
-    <row r="501">
-      <c r="A501" s="9"/>
-      <c r="B501" s="9"/>
+    <row r="501" spans="3:3">
       <c r="C501" s="9"/>
     </row>
-    <row r="502">
-      <c r="A502" s="9"/>
-      <c r="B502" s="9"/>
+    <row r="502" spans="3:3">
       <c r="C502" s="9"/>
     </row>
-    <row r="503">
-      <c r="A503" s="9"/>
-      <c r="B503" s="9"/>
+    <row r="503" spans="3:3">
       <c r="C503" s="9"/>
     </row>
-    <row r="504">
-      <c r="A504" s="9"/>
-      <c r="B504" s="9"/>
+    <row r="504" spans="3:3">
       <c r="C504" s="9"/>
     </row>
-    <row r="505">
-      <c r="A505" s="9"/>
-      <c r="B505" s="9"/>
+    <row r="505" spans="3:3">
       <c r="C505" s="9"/>
     </row>
-    <row r="506">
-      <c r="A506" s="9"/>
-      <c r="B506" s="9"/>
+    <row r="506" spans="3:3">
       <c r="C506" s="9"/>
     </row>
-    <row r="507">
-      <c r="A507" s="9"/>
-      <c r="B507" s="9"/>
+    <row r="507" spans="3:3">
       <c r="C507" s="9"/>
     </row>
-    <row r="508">
-      <c r="A508" s="9"/>
-      <c r="B508" s="9"/>
+    <row r="508" spans="3:3">
       <c r="C508" s="9"/>
     </row>
-    <row r="509">
-      <c r="A509" s="9"/>
-      <c r="B509" s="9"/>
+    <row r="509" spans="3:3">
       <c r="C509" s="9"/>
     </row>
-    <row r="510">
-      <c r="A510" s="9"/>
-      <c r="B510" s="9"/>
+    <row r="510" spans="3:3">
       <c r="C510" s="9"/>
     </row>
-    <row r="511">
-      <c r="A511" s="9"/>
-      <c r="B511" s="9"/>
+    <row r="511" spans="3:3">
       <c r="C511" s="9"/>
     </row>
-    <row r="512">
-      <c r="A512" s="9"/>
-      <c r="B512" s="9"/>
+    <row r="512" spans="3:3">
       <c r="C512" s="9"/>
     </row>
-    <row r="513">
-      <c r="A513" s="9"/>
-      <c r="B513" s="9"/>
+    <row r="513" spans="3:3">
       <c r="C513" s="9"/>
     </row>
-    <row r="514">
-      <c r="A514" s="9"/>
-      <c r="B514" s="9"/>
+    <row r="514" spans="3:3">
       <c r="C514" s="9"/>
     </row>
-    <row r="515">
-      <c r="A515" s="9"/>
-      <c r="B515" s="9"/>
+    <row r="515" spans="3:3">
       <c r="C515" s="9"/>
     </row>
-    <row r="516">
-      <c r="A516" s="9"/>
-      <c r="B516" s="9"/>
+    <row r="516" spans="3:3">
       <c r="C516" s="9"/>
     </row>
-    <row r="517">
-      <c r="A517" s="9"/>
-      <c r="B517" s="9"/>
+    <row r="517" spans="3:3">
       <c r="C517" s="9"/>
     </row>
-    <row r="518">
-      <c r="A518" s="9"/>
-      <c r="B518" s="9"/>
+    <row r="518" spans="3:3">
       <c r="C518" s="9"/>
     </row>
-    <row r="519">
-      <c r="A519" s="9"/>
-      <c r="B519" s="9"/>
+    <row r="519" spans="3:3">
       <c r="C519" s="9"/>
     </row>
-    <row r="520">
-      <c r="A520" s="9"/>
-      <c r="B520" s="9"/>
+    <row r="520" spans="3:3">
       <c r="C520" s="9"/>
     </row>
-    <row r="521">
-      <c r="A521" s="9"/>
-      <c r="B521" s="9"/>
+    <row r="521" spans="3:3">
       <c r="C521" s="9"/>
     </row>
-    <row r="522">
-      <c r="A522" s="9"/>
-      <c r="B522" s="9"/>
+    <row r="522" spans="3:3">
       <c r="C522" s="9"/>
     </row>
-    <row r="523">
-      <c r="A523" s="9"/>
-      <c r="B523" s="9"/>
+    <row r="523" spans="3:3">
       <c r="C523" s="9"/>
     </row>
-    <row r="524">
-      <c r="A524" s="9"/>
-      <c r="B524" s="9"/>
+    <row r="524" spans="3:3">
       <c r="C524" s="9"/>
     </row>
-    <row r="525">
-      <c r="A525" s="9"/>
-      <c r="B525" s="9"/>
+    <row r="525" spans="3:3">
       <c r="C525" s="9"/>
     </row>
-    <row r="526">
-      <c r="A526" s="9"/>
-      <c r="B526" s="9"/>
+    <row r="526" spans="3:3">
       <c r="C526" s="9"/>
     </row>
-    <row r="527">
-      <c r="A527" s="9"/>
-      <c r="B527" s="9"/>
+    <row r="527" spans="3:3">
       <c r="C527" s="9"/>
     </row>
-    <row r="528">
-      <c r="A528" s="9"/>
-      <c r="B528" s="9"/>
+    <row r="528" spans="3:3">
       <c r="C528" s="9"/>
     </row>
-    <row r="529">
-      <c r="A529" s="9"/>
-      <c r="B529" s="9"/>
+    <row r="529" spans="3:3">
       <c r="C529" s="9"/>
     </row>
-    <row r="530">
-      <c r="A530" s="9"/>
-      <c r="B530" s="9"/>
+    <row r="530" spans="3:3">
       <c r="C530" s="9"/>
     </row>
-    <row r="531">
-      <c r="A531" s="9"/>
-      <c r="B531" s="9"/>
+    <row r="531" spans="3:3">
       <c r="C531" s="9"/>
     </row>
-    <row r="532">
-      <c r="A532" s="9"/>
-      <c r="B532" s="9"/>
+    <row r="532" spans="3:3">
       <c r="C532" s="9"/>
     </row>
-    <row r="533">
-      <c r="A533" s="9"/>
-      <c r="B533" s="9"/>
+    <row r="533" spans="3:3">
       <c r="C533" s="9"/>
     </row>
-    <row r="534">
-      <c r="A534" s="9"/>
-      <c r="B534" s="9"/>
+    <row r="534" spans="3:3">
       <c r="C534" s="9"/>
     </row>
-    <row r="535">
-      <c r="A535" s="9"/>
-      <c r="B535" s="9"/>
+    <row r="535" spans="3:3">
       <c r="C535" s="9"/>
     </row>
-    <row r="536">
-      <c r="A536" s="9"/>
-      <c r="B536" s="9"/>
+    <row r="536" spans="3:3">
       <c r="C536" s="9"/>
     </row>
-    <row r="537">
-      <c r="A537" s="9"/>
-      <c r="B537" s="9"/>
+    <row r="537" spans="3:3">
       <c r="C537" s="9"/>
     </row>
-    <row r="538">
-      <c r="A538" s="9"/>
-      <c r="B538" s="9"/>
+    <row r="538" spans="3:3">
       <c r="C538" s="9"/>
     </row>
-    <row r="539">
-      <c r="A539" s="9"/>
-      <c r="B539" s="9"/>
+    <row r="539" spans="3:3">
       <c r="C539" s="9"/>
     </row>
-    <row r="540">
-      <c r="A540" s="9"/>
-      <c r="B540" s="9"/>
+    <row r="540" spans="3:3">
       <c r="C540" s="9"/>
     </row>
-    <row r="541">
-      <c r="A541" s="9"/>
-      <c r="B541" s="9"/>
+    <row r="541" spans="3:3">
       <c r="C541" s="9"/>
     </row>
-    <row r="542">
-      <c r="A542" s="9"/>
-      <c r="B542" s="9"/>
+    <row r="542" spans="3:3">
       <c r="C542" s="9"/>
     </row>
-    <row r="543">
-      <c r="A543" s="9"/>
-      <c r="B543" s="9"/>
+    <row r="543" spans="3:3">
       <c r="C543" s="9"/>
     </row>
-    <row r="544">
-      <c r="A544" s="9"/>
-      <c r="B544" s="9"/>
+    <row r="544" spans="3:3">
       <c r="C544" s="9"/>
     </row>
-    <row r="545">
-      <c r="A545" s="9"/>
-      <c r="B545" s="9"/>
+    <row r="545" spans="3:3">
       <c r="C545" s="9"/>
     </row>
-    <row r="546">
-      <c r="A546" s="9"/>
-      <c r="B546" s="9"/>
+    <row r="546" spans="3:3">
       <c r="C546" s="9"/>
     </row>
-    <row r="547">
-      <c r="A547" s="9"/>
-      <c r="B547" s="9"/>
+    <row r="547" spans="3:3">
       <c r="C547" s="9"/>
     </row>
-    <row r="548">
-      <c r="A548" s="9"/>
-      <c r="B548" s="9"/>
+    <row r="548" spans="3:3">
       <c r="C548" s="9"/>
     </row>
-    <row r="549">
-      <c r="A549" s="9"/>
-      <c r="B549" s="9"/>
+    <row r="549" spans="3:3">
       <c r="C549" s="9"/>
     </row>
-    <row r="550">
-      <c r="A550" s="9"/>
-      <c r="B550" s="9"/>
+    <row r="550" spans="3:3">
       <c r="C550" s="9"/>
     </row>
-    <row r="551">
-      <c r="A551" s="9"/>
-      <c r="B551" s="9"/>
+    <row r="551" spans="3:3">
       <c r="C551" s="9"/>
     </row>
-    <row r="552">
-      <c r="A552" s="9"/>
-      <c r="B552" s="9"/>
+    <row r="552" spans="3:3">
       <c r="C552" s="9"/>
     </row>
-    <row r="553">
-      <c r="A553" s="9"/>
-      <c r="B553" s="9"/>
+    <row r="553" spans="3:3">
       <c r="C553" s="9"/>
     </row>
-    <row r="554">
-      <c r="A554" s="9"/>
-      <c r="B554" s="9"/>
+    <row r="554" spans="3:3">
       <c r="C554" s="9"/>
     </row>
-    <row r="555">
-      <c r="A555" s="9"/>
-      <c r="B555" s="9"/>
+    <row r="555" spans="3:3">
       <c r="C555" s="9"/>
     </row>
-    <row r="556">
-      <c r="A556" s="9"/>
-      <c r="B556" s="9"/>
+    <row r="556" spans="3:3">
       <c r="C556" s="9"/>
     </row>
-    <row r="557">
-      <c r="A557" s="9"/>
-      <c r="B557" s="9"/>
+    <row r="557" spans="3:3">
       <c r="C557" s="9"/>
     </row>
-    <row r="558">
-      <c r="A558" s="9"/>
-      <c r="B558" s="9"/>
+    <row r="558" spans="3:3">
       <c r="C558" s="9"/>
     </row>
-    <row r="559">
-      <c r="A559" s="9"/>
-      <c r="B559" s="9"/>
+    <row r="559" spans="3:3">
       <c r="C559" s="9"/>
     </row>
-    <row r="560">
-      <c r="A560" s="9"/>
-      <c r="B560" s="9"/>
+    <row r="560" spans="3:3">
       <c r="C560" s="9"/>
     </row>
-    <row r="561">
-      <c r="A561" s="9"/>
-      <c r="B561" s="9"/>
+    <row r="561" spans="3:3">
       <c r="C561" s="9"/>
     </row>
-    <row r="562">
-      <c r="A562" s="9"/>
-      <c r="B562" s="9"/>
+    <row r="562" spans="3:3">
       <c r="C562" s="9"/>
     </row>
-    <row r="563">
-      <c r="A563" s="9"/>
-      <c r="B563" s="9"/>
+    <row r="563" spans="3:3">
       <c r="C563" s="9"/>
     </row>
-    <row r="564">
-      <c r="A564" s="9"/>
-      <c r="B564" s="9"/>
+    <row r="564" spans="3:3">
       <c r="C564" s="9"/>
     </row>
-    <row r="565">
-      <c r="A565" s="9"/>
-      <c r="B565" s="9"/>
+    <row r="565" spans="3:3">
       <c r="C565" s="9"/>
     </row>
-    <row r="566">
-      <c r="A566" s="9"/>
-      <c r="B566" s="9"/>
+    <row r="566" spans="3:3">
       <c r="C566" s="9"/>
     </row>
-    <row r="567">
-      <c r="A567" s="9"/>
-      <c r="B567" s="9"/>
+    <row r="567" spans="3:3">
       <c r="C567" s="9"/>
     </row>
-    <row r="568">
-      <c r="A568" s="9"/>
-      <c r="B568" s="9"/>
+    <row r="568" spans="3:3">
       <c r="C568" s="9"/>
     </row>
-    <row r="569">
-      <c r="A569" s="9"/>
-      <c r="B569" s="9"/>
+    <row r="569" spans="3:3">
       <c r="C569" s="9"/>
     </row>
-    <row r="570">
-      <c r="A570" s="9"/>
-      <c r="B570" s="9"/>
+    <row r="570" spans="3:3">
       <c r="C570" s="9"/>
     </row>
-    <row r="571">
-      <c r="A571" s="9"/>
-      <c r="B571" s="9"/>
+    <row r="571" spans="3:3">
       <c r="C571" s="9"/>
     </row>
-    <row r="572">
-      <c r="A572" s="9"/>
-      <c r="B572" s="9"/>
+    <row r="572" spans="3:3">
       <c r="C572" s="9"/>
     </row>
-    <row r="573">
-      <c r="A573" s="9"/>
-      <c r="B573" s="9"/>
+    <row r="573" spans="3:3">
       <c r="C573" s="9"/>
     </row>
-    <row r="574">
-      <c r="A574" s="9"/>
-      <c r="B574" s="9"/>
+    <row r="574" spans="3:3">
       <c r="C574" s="9"/>
     </row>
-    <row r="575">
-      <c r="A575" s="9"/>
-      <c r="B575" s="9"/>
+    <row r="575" spans="3:3">
       <c r="C575" s="9"/>
     </row>
-    <row r="576">
-      <c r="A576" s="9"/>
-      <c r="B576" s="9"/>
+    <row r="576" spans="3:3">
       <c r="C576" s="9"/>
     </row>
-    <row r="577">
-      <c r="A577" s="9"/>
-      <c r="B577" s="9"/>
+    <row r="577" spans="3:3">
       <c r="C577" s="9"/>
     </row>
-    <row r="578">
-      <c r="A578" s="9"/>
-      <c r="B578" s="9"/>
+    <row r="578" spans="3:3">
       <c r="C578" s="9"/>
     </row>
-    <row r="579">
-      <c r="A579" s="9"/>
-      <c r="B579" s="9"/>
+    <row r="579" spans="3:3">
       <c r="C579" s="9"/>
     </row>
-    <row r="580">
-      <c r="A580" s="9"/>
-      <c r="B580" s="9"/>
+    <row r="580" spans="3:3">
       <c r="C580" s="9"/>
     </row>
-    <row r="581">
-      <c r="A581" s="9"/>
-      <c r="B581" s="9"/>
+    <row r="581" spans="3:3">
       <c r="C581" s="9"/>
     </row>
-    <row r="582">
-      <c r="A582" s="9"/>
-      <c r="B582" s="9"/>
+    <row r="582" spans="3:3">
       <c r="C582" s="9"/>
     </row>
-    <row r="583">
-      <c r="A583" s="9"/>
-      <c r="B583" s="9"/>
+    <row r="583" spans="3:3">
       <c r="C583" s="9"/>
     </row>
-    <row r="584">
-      <c r="A584" s="9"/>
-      <c r="B584" s="9"/>
+    <row r="584" spans="3:3">
       <c r="C584" s="9"/>
     </row>
-    <row r="585">
-      <c r="A585" s="9"/>
-      <c r="B585" s="9"/>
+    <row r="585" spans="3:3">
       <c r="C585" s="9"/>
     </row>
-    <row r="586">
-      <c r="A586" s="9"/>
-      <c r="B586" s="9"/>
+    <row r="586" spans="3:3">
       <c r="C586" s="9"/>
     </row>
-    <row r="587">
-      <c r="A587" s="9"/>
-      <c r="B587" s="9"/>
+    <row r="587" spans="3:3">
       <c r="C587" s="9"/>
     </row>
-    <row r="588">
-      <c r="A588" s="9"/>
-      <c r="B588" s="9"/>
+    <row r="588" spans="3:3">
       <c r="C588" s="9"/>
     </row>
-    <row r="589">
-      <c r="A589" s="9"/>
-      <c r="B589" s="9"/>
+    <row r="589" spans="3:3">
       <c r="C589" s="9"/>
     </row>
-    <row r="590">
-      <c r="A590" s="9"/>
-      <c r="B590" s="9"/>
+    <row r="590" spans="3:3">
       <c r="C590" s="9"/>
     </row>
-    <row r="591">
-      <c r="A591" s="9"/>
-      <c r="B591" s="9"/>
+    <row r="591" spans="3:3">
       <c r="C591" s="9"/>
     </row>
-    <row r="592">
-      <c r="A592" s="9"/>
-      <c r="B592" s="9"/>
+    <row r="592" spans="3:3">
       <c r="C592" s="9"/>
     </row>
-    <row r="593">
-      <c r="A593" s="9"/>
-      <c r="B593" s="9"/>
+    <row r="593" spans="3:3">
       <c r="C593" s="9"/>
     </row>
-    <row r="594">
-      <c r="A594" s="9"/>
-      <c r="B594" s="9"/>
+    <row r="594" spans="3:3">
       <c r="C594" s="9"/>
     </row>
-    <row r="595">
-      <c r="A595" s="9"/>
-      <c r="B595" s="9"/>
+    <row r="595" spans="3:3">
       <c r="C595" s="9"/>
     </row>
-    <row r="596">
-      <c r="A596" s="9"/>
-      <c r="B596" s="9"/>
+    <row r="596" spans="3:3">
       <c r="C596" s="9"/>
     </row>
-    <row r="597">
-      <c r="A597" s="9"/>
-      <c r="B597" s="9"/>
+    <row r="597" spans="3:3">
       <c r="C597" s="9"/>
     </row>
-    <row r="598">
-      <c r="A598" s="9"/>
-      <c r="B598" s="9"/>
+    <row r="598" spans="3:3">
       <c r="C598" s="9"/>
     </row>
-    <row r="599">
-      <c r="A599" s="9"/>
-      <c r="B599" s="9"/>
+    <row r="599" spans="3:3">
       <c r="C599" s="9"/>
     </row>
-    <row r="600">
-      <c r="A600" s="9"/>
-      <c r="B600" s="9"/>
+    <row r="600" spans="3:3">
       <c r="C600" s="9"/>
     </row>
-    <row r="601">
-      <c r="A601" s="9"/>
-      <c r="B601" s="9"/>
+    <row r="601" spans="3:3">
       <c r="C601" s="9"/>
     </row>
-    <row r="602">
-      <c r="A602" s="9"/>
-      <c r="B602" s="9"/>
+    <row r="602" spans="3:3">
       <c r="C602" s="9"/>
     </row>
-    <row r="603">
-      <c r="A603" s="9"/>
-      <c r="B603" s="9"/>
+    <row r="603" spans="3:3">
       <c r="C603" s="9"/>
     </row>
-    <row r="604">
-      <c r="A604" s="9"/>
-      <c r="B604" s="9"/>
+    <row r="604" spans="3:3">
       <c r="C604" s="9"/>
     </row>
-    <row r="605">
-      <c r="A605" s="9"/>
-      <c r="B605" s="9"/>
+    <row r="605" spans="3:3">
       <c r="C605" s="9"/>
     </row>
-    <row r="606">
-      <c r="A606" s="9"/>
-      <c r="B606" s="9"/>
+    <row r="606" spans="3:3">
       <c r="C606" s="9"/>
     </row>
-    <row r="607">
-      <c r="A607" s="9"/>
-      <c r="B607" s="9"/>
+    <row r="607" spans="3:3">
       <c r="C607" s="9"/>
     </row>
-    <row r="608">
-      <c r="A608" s="9"/>
-      <c r="B608" s="9"/>
+    <row r="608" spans="3:3">
       <c r="C608" s="9"/>
     </row>
-    <row r="609">
-      <c r="A609" s="9"/>
-      <c r="B609" s="9"/>
+    <row r="609" spans="3:3">
       <c r="C609" s="9"/>
     </row>
-    <row r="610">
-      <c r="A610" s="9"/>
-      <c r="B610" s="9"/>
+    <row r="610" spans="3:3">
       <c r="C610" s="9"/>
     </row>
-    <row r="611">
-      <c r="A611" s="9"/>
-      <c r="B611" s="9"/>
+    <row r="611" spans="3:3">
       <c r="C611" s="9"/>
     </row>
-    <row r="612">
-      <c r="A612" s="9"/>
-      <c r="B612" s="9"/>
+    <row r="612" spans="3:3">
       <c r="C612" s="9"/>
     </row>
-    <row r="613">
-      <c r="A613" s="9"/>
-      <c r="B613" s="9"/>
+    <row r="613" spans="3:3">
       <c r="C613" s="9"/>
     </row>
-    <row r="614">
-      <c r="A614" s="9"/>
-      <c r="B614" s="9"/>
+    <row r="614" spans="3:3">
       <c r="C614" s="9"/>
     </row>
-    <row r="615">
-      <c r="A615" s="9"/>
-      <c r="B615" s="9"/>
+    <row r="615" spans="3:3">
       <c r="C615" s="9"/>
     </row>
-    <row r="616">
-      <c r="A616" s="9"/>
-      <c r="B616" s="9"/>
+    <row r="616" spans="3:3">
       <c r="C616" s="9"/>
     </row>
-    <row r="617">
-      <c r="A617" s="9"/>
-      <c r="B617" s="9"/>
+    <row r="617" spans="3:3">
       <c r="C617" s="9"/>
     </row>
-    <row r="618">
-      <c r="A618" s="9"/>
-      <c r="B618" s="9"/>
+    <row r="618" spans="3:3">
       <c r="C618" s="9"/>
     </row>
-    <row r="619">
-      <c r="A619" s="9"/>
-      <c r="B619" s="9"/>
+    <row r="619" spans="3:3">
       <c r="C619" s="9"/>
     </row>
-    <row r="620">
-      <c r="A620" s="9"/>
-      <c r="B620" s="9"/>
+    <row r="620" spans="3:3">
       <c r="C620" s="9"/>
     </row>
-    <row r="621">
-      <c r="A621" s="9"/>
-      <c r="B621" s="9"/>
+    <row r="621" spans="3:3">
       <c r="C621" s="9"/>
     </row>
-    <row r="622">
-      <c r="A622" s="9"/>
-      <c r="B622" s="9"/>
+    <row r="622" spans="3:3">
       <c r="C622" s="9"/>
     </row>
-    <row r="623">
-      <c r="A623" s="9"/>
-      <c r="B623" s="9"/>
+    <row r="623" spans="3:3">
       <c r="C623" s="9"/>
     </row>
-    <row r="624">
-      <c r="A624" s="9"/>
-      <c r="B624" s="9"/>
+    <row r="624" spans="3:3">
       <c r="C624" s="9"/>
     </row>
-    <row r="625">
-      <c r="A625" s="9"/>
-      <c r="B625" s="9"/>
+    <row r="625" spans="3:3">
       <c r="C625" s="9"/>
     </row>
-    <row r="626">
-      <c r="A626" s="9"/>
-      <c r="B626" s="9"/>
+    <row r="626" spans="3:3">
       <c r="C626" s="9"/>
     </row>
-    <row r="627">
-      <c r="A627" s="9"/>
-      <c r="B627" s="9"/>
+    <row r="627" spans="3:3">
       <c r="C627" s="9"/>
     </row>
-    <row r="628">
-      <c r="A628" s="9"/>
-      <c r="B628" s="9"/>
+    <row r="628" spans="3:3">
       <c r="C628" s="9"/>
     </row>
-    <row r="629">
-      <c r="A629" s="9"/>
-      <c r="B629" s="9"/>
+    <row r="629" spans="3:3">
       <c r="C629" s="9"/>
     </row>
-    <row r="630">
-      <c r="A630" s="9"/>
-      <c r="B630" s="9"/>
+    <row r="630" spans="3:3">
       <c r="C630" s="9"/>
     </row>
-    <row r="631">
-      <c r="A631" s="9"/>
-      <c r="B631" s="9"/>
+    <row r="631" spans="3:3">
       <c r="C631" s="9"/>
     </row>
-    <row r="632">
-      <c r="A632" s="9"/>
-      <c r="B632" s="9"/>
+    <row r="632" spans="3:3">
       <c r="C632" s="9"/>
     </row>
-    <row r="633">
-      <c r="A633" s="9"/>
-      <c r="B633" s="9"/>
+    <row r="633" spans="3:3">
       <c r="C633" s="9"/>
     </row>
-    <row r="634">
-      <c r="A634" s="9"/>
-      <c r="B634" s="9"/>
+    <row r="634" spans="3:3">
       <c r="C634" s="9"/>
     </row>
-    <row r="635">
-      <c r="A635" s="9"/>
-      <c r="B635" s="9"/>
+    <row r="635" spans="3:3">
       <c r="C635" s="9"/>
     </row>
-    <row r="636">
-      <c r="A636" s="9"/>
-      <c r="B636" s="9"/>
+    <row r="636" spans="3:3">
       <c r="C636" s="9"/>
     </row>
-    <row r="637">
-      <c r="A637" s="9"/>
-      <c r="B637" s="9"/>
+    <row r="637" spans="3:3">
       <c r="C637" s="9"/>
     </row>
-    <row r="638">
-      <c r="A638" s="9"/>
-      <c r="B638" s="9"/>
+    <row r="638" spans="3:3">
       <c r="C638" s="9"/>
     </row>
-    <row r="639">
-      <c r="A639" s="9"/>
-      <c r="B639" s="9"/>
+    <row r="639" spans="3:3">
       <c r="C639" s="9"/>
     </row>
-    <row r="640">
-      <c r="A640" s="9"/>
-      <c r="B640" s="9"/>
+    <row r="640" spans="3:3">
       <c r="C640" s="9"/>
     </row>
-    <row r="641">
-      <c r="A641" s="9"/>
-      <c r="B641" s="9"/>
+    <row r="641" spans="3:3">
       <c r="C641" s="9"/>
     </row>
-    <row r="642">
-      <c r="A642" s="9"/>
-      <c r="B642" s="9"/>
+    <row r="642" spans="3:3">
       <c r="C642" s="9"/>
     </row>
-    <row r="643">
-      <c r="A643" s="9"/>
-      <c r="B643" s="9"/>
+    <row r="643" spans="3:3">
       <c r="C643" s="9"/>
     </row>
-    <row r="644">
-      <c r="A644" s="9"/>
-      <c r="B644" s="9"/>
+    <row r="644" spans="3:3">
       <c r="C644" s="9"/>
     </row>
-    <row r="645">
-      <c r="A645" s="9"/>
-      <c r="B645" s="9"/>
+    <row r="645" spans="3:3">
       <c r="C645" s="9"/>
     </row>
-    <row r="646">
-      <c r="A646" s="9"/>
-      <c r="B646" s="9"/>
+    <row r="646" spans="3:3">
       <c r="C646" s="9"/>
     </row>
-    <row r="647">
-      <c r="A647" s="9"/>
-      <c r="B647" s="9"/>
+    <row r="647" spans="3:3">
       <c r="C647" s="9"/>
     </row>
-    <row r="648">
-      <c r="A648" s="9"/>
-      <c r="B648" s="9"/>
+    <row r="648" spans="3:3">
       <c r="C648" s="9"/>
     </row>
-    <row r="649">
-      <c r="A649" s="9"/>
-      <c r="B649" s="9"/>
+    <row r="649" spans="3:3">
       <c r="C649" s="9"/>
     </row>
-    <row r="650">
-      <c r="A650" s="9"/>
-      <c r="B650" s="9"/>
+    <row r="650" spans="3:3">
       <c r="C650" s="9"/>
     </row>
-    <row r="651">
-      <c r="A651" s="9"/>
-      <c r="B651" s="9"/>
+    <row r="651" spans="3:3">
       <c r="C651" s="9"/>
     </row>
-    <row r="652">
-      <c r="A652" s="9"/>
-      <c r="B652" s="9"/>
+    <row r="652" spans="3:3">
       <c r="C652" s="9"/>
     </row>
-    <row r="653">
-      <c r="A653" s="9"/>
-      <c r="B653" s="9"/>
+    <row r="653" spans="3:3">
       <c r="C653" s="9"/>
     </row>
-    <row r="654">
-      <c r="A654" s="9"/>
-      <c r="B654" s="9"/>
+    <row r="654" spans="3:3">
       <c r="C654" s="9"/>
     </row>
-    <row r="655">
-      <c r="A655" s="9"/>
-      <c r="B655" s="9"/>
+    <row r="655" spans="3:3">
       <c r="C655" s="9"/>
     </row>
-    <row r="656">
-      <c r="A656" s="9"/>
-      <c r="B656" s="9"/>
+    <row r="656" spans="3:3">
       <c r="C656" s="9"/>
     </row>
-    <row r="657">
-      <c r="A657" s="9"/>
-      <c r="B657" s="9"/>
+    <row r="657" spans="3:3">
       <c r="C657" s="9"/>
     </row>
-    <row r="658">
-      <c r="A658" s="9"/>
-      <c r="B658" s="9"/>
+    <row r="658" spans="3:3">
       <c r="C658" s="9"/>
     </row>
-    <row r="659">
-      <c r="A659" s="9"/>
-      <c r="B659" s="9"/>
+    <row r="659" spans="3:3">
       <c r="C659" s="9"/>
     </row>
-    <row r="660">
-      <c r="A660" s="9"/>
-      <c r="B660" s="9"/>
+    <row r="660" spans="3:3">
       <c r="C660" s="9"/>
     </row>
-    <row r="661">
-      <c r="A661" s="9"/>
-      <c r="B661" s="9"/>
+    <row r="661" spans="3:3">
       <c r="C661" s="9"/>
     </row>
-    <row r="662">
-      <c r="A662" s="9"/>
-      <c r="B662" s="9"/>
+    <row r="662" spans="3:3">
       <c r="C662" s="9"/>
     </row>
-    <row r="663">
-      <c r="A663" s="9"/>
-      <c r="B663" s="9"/>
+    <row r="663" spans="3:3">
       <c r="C663" s="9"/>
     </row>
-    <row r="664">
-      <c r="A664" s="9"/>
-      <c r="B664" s="9"/>
+    <row r="664" spans="3:3">
       <c r="C664" s="9"/>
     </row>
-    <row r="665">
-      <c r="A665" s="9"/>
-      <c r="B665" s="9"/>
+    <row r="665" spans="3:3">
       <c r="C665" s="9"/>
     </row>
-    <row r="666">
-      <c r="A666" s="9"/>
-      <c r="B666" s="9"/>
+    <row r="666" spans="3:3">
       <c r="C666" s="9"/>
     </row>
-    <row r="667">
-      <c r="A667" s="9"/>
-      <c r="B667" s="9"/>
+    <row r="667" spans="3:3">
       <c r="C667" s="9"/>
     </row>
-    <row r="668">
-      <c r="A668" s="9"/>
-      <c r="B668" s="9"/>
+    <row r="668" spans="3:3">
       <c r="C668" s="9"/>
     </row>
-    <row r="669">
-      <c r="A669" s="9"/>
-      <c r="B669" s="9"/>
+    <row r="669" spans="3:3">
       <c r="C669" s="9"/>
     </row>
-    <row r="670">
-      <c r="A670" s="9"/>
-      <c r="B670" s="9"/>
+    <row r="670" spans="3:3">
       <c r="C670" s="9"/>
     </row>
-    <row r="671">
-      <c r="A671" s="9"/>
-      <c r="B671" s="9"/>
+    <row r="671" spans="3:3">
       <c r="C671" s="9"/>
     </row>
-    <row r="672">
-      <c r="A672" s="9"/>
-      <c r="B672" s="9"/>
+    <row r="672" spans="3:3">
       <c r="C672" s="9"/>
     </row>
-    <row r="673">
-      <c r="A673" s="9"/>
-      <c r="B673" s="9"/>
+    <row r="673" spans="3:3">
       <c r="C673" s="9"/>
     </row>
-    <row r="674">
-      <c r="A674" s="9"/>
-      <c r="B674" s="9"/>
+    <row r="674" spans="3:3">
       <c r="C674" s="9"/>
     </row>
-    <row r="675">
-      <c r="A675" s="9"/>
-      <c r="B675" s="9"/>
+    <row r="675" spans="3:3">
       <c r="C675" s="9"/>
     </row>
-    <row r="676">
-      <c r="A676" s="9"/>
-      <c r="B676" s="9"/>
+    <row r="676" spans="3:3">
       <c r="C676" s="9"/>
     </row>
-    <row r="677">
-      <c r="A677" s="9"/>
-      <c r="B677" s="9"/>
+    <row r="677" spans="3:3">
       <c r="C677" s="9"/>
     </row>
-    <row r="678">
-      <c r="A678" s="9"/>
-      <c r="B678" s="9"/>
+    <row r="678" spans="3:3">
       <c r="C678" s="9"/>
     </row>
-    <row r="679">
-      <c r="A679" s="9"/>
-      <c r="B679" s="9"/>
+    <row r="679" spans="3:3">
       <c r="C679" s="9"/>
     </row>
-    <row r="680">
-      <c r="A680" s="9"/>
-      <c r="B680" s="9"/>
+    <row r="680" spans="3:3">
       <c r="C680" s="9"/>
     </row>
-    <row r="681">
-      <c r="A681" s="9"/>
-      <c r="B681" s="9"/>
+    <row r="681" spans="3:3">
       <c r="C681" s="9"/>
     </row>
-    <row r="682">
-      <c r="A682" s="9"/>
-      <c r="B682" s="9"/>
+    <row r="682" spans="3:3">
       <c r="C682" s="9"/>
     </row>
-    <row r="683">
-      <c r="A683" s="9"/>
-      <c r="B683" s="9"/>
+    <row r="683" spans="3:3">
       <c r="C683" s="9"/>
     </row>
-    <row r="684">
-      <c r="A684" s="9"/>
-      <c r="B684" s="9"/>
+    <row r="684" spans="3:3">
       <c r="C684" s="9"/>
     </row>
-    <row r="685">
-      <c r="A685" s="9"/>
-      <c r="B685" s="9"/>
+    <row r="685" spans="3:3">
       <c r="C685" s="9"/>
     </row>
-    <row r="686">
-      <c r="A686" s="9"/>
-      <c r="B686" s="9"/>
+    <row r="686" spans="3:3">
       <c r="C686" s="9"/>
     </row>
-    <row r="687">
-      <c r="A687" s="9"/>
-      <c r="B687" s="9"/>
+    <row r="687" spans="3:3">
       <c r="C687" s="9"/>
     </row>
-    <row r="688">
-      <c r="A688" s="9"/>
-      <c r="B688" s="9"/>
+    <row r="688" spans="3:3">
       <c r="C688" s="9"/>
     </row>
-    <row r="689">
-      <c r="A689" s="9"/>
-      <c r="B689" s="9"/>
+    <row r="689" spans="3:3">
       <c r="C689" s="9"/>
     </row>
-    <row r="690">
-      <c r="A690" s="9"/>
-      <c r="B690" s="9"/>
+    <row r="690" spans="3:3">
       <c r="C690" s="9"/>
     </row>
-    <row r="691">
-      <c r="A691" s="9"/>
-      <c r="B691" s="9"/>
+    <row r="691" spans="3:3">
       <c r="C691" s="9"/>
     </row>
-    <row r="692">
-      <c r="A692" s="9"/>
-      <c r="B692" s="9"/>
+    <row r="692" spans="3:3">
       <c r="C692" s="9"/>
     </row>
-    <row r="693">
-      <c r="A693" s="9"/>
-      <c r="B693" s="9"/>
+    <row r="693" spans="3:3">
       <c r="C693" s="9"/>
     </row>
-    <row r="694">
-      <c r="A694" s="9"/>
-      <c r="B694" s="9"/>
+    <row r="694" spans="3:3">
       <c r="C694" s="9"/>
     </row>
-    <row r="695">
-      <c r="A695" s="9"/>
-      <c r="B695" s="9"/>
+    <row r="695" spans="3:3">
       <c r="C695" s="9"/>
     </row>
-    <row r="696">
-      <c r="A696" s="9"/>
-      <c r="B696" s="9"/>
+    <row r="696" spans="3:3">
       <c r="C696" s="9"/>
     </row>
-    <row r="697">
-      <c r="A697" s="9"/>
-      <c r="B697" s="9"/>
+    <row r="697" spans="3:3">
       <c r="C697" s="9"/>
     </row>
-    <row r="698">
-      <c r="A698" s="9"/>
-      <c r="B698" s="9"/>
+    <row r="698" spans="3:3">
       <c r="C698" s="9"/>
     </row>
-    <row r="699">
-      <c r="A699" s="9"/>
-      <c r="B699" s="9"/>
+    <row r="699" spans="3:3">
       <c r="C699" s="9"/>
     </row>
-    <row r="700">
-      <c r="A700" s="9"/>
-      <c r="B700" s="9"/>
+    <row r="700" spans="3:3">
       <c r="C700" s="9"/>
     </row>
-    <row r="701">
-      <c r="A701" s="9"/>
-      <c r="B701" s="9"/>
+    <row r="701" spans="3:3">
       <c r="C701" s="9"/>
     </row>
-    <row r="702">
-      <c r="A702" s="9"/>
-      <c r="B702" s="9"/>
+    <row r="702" spans="3:3">
       <c r="C702" s="9"/>
     </row>
-    <row r="703">
-      <c r="A703" s="9"/>
-      <c r="B703" s="9"/>
+    <row r="703" spans="3:3">
       <c r="C703" s="9"/>
     </row>
-    <row r="704">
-      <c r="A704" s="9"/>
-      <c r="B704" s="9"/>
+    <row r="704" spans="3:3">
       <c r="C704" s="9"/>
     </row>
-    <row r="705">
-      <c r="A705" s="9"/>
-      <c r="B705" s="9"/>
+    <row r="705" spans="3:3">
       <c r="C705" s="9"/>
     </row>
-    <row r="706">
-      <c r="A706" s="9"/>
-      <c r="B706" s="9"/>
+    <row r="706" spans="3:3">
       <c r="C706" s="9"/>
     </row>
-    <row r="707">
-      <c r="A707" s="9"/>
-      <c r="B707" s="9"/>
+    <row r="707" spans="3:3">
       <c r="C707" s="9"/>
     </row>
-    <row r="708">
-      <c r="A708" s="9"/>
-      <c r="B708" s="9"/>
+    <row r="708" spans="3:3">
       <c r="C708" s="9"/>
     </row>
-    <row r="709">
-      <c r="A709" s="9"/>
-      <c r="B709" s="9"/>
+    <row r="709" spans="3:3">
       <c r="C709" s="9"/>
     </row>
-    <row r="710">
-      <c r="A710" s="9"/>
-      <c r="B710" s="9"/>
+    <row r="710" spans="3:3">
       <c r="C710" s="9"/>
     </row>
-    <row r="711">
-      <c r="A711" s="9"/>
-      <c r="B711" s="9"/>
+    <row r="711" spans="3:3">
       <c r="C711" s="9"/>
     </row>
-    <row r="712">
-      <c r="A712" s="9"/>
-      <c r="B712" s="9"/>
+    <row r="712" spans="3:3">
       <c r="C712" s="9"/>
     </row>
-    <row r="713">
-      <c r="A713" s="9"/>
-      <c r="B713" s="9"/>
+    <row r="713" spans="3:3">
       <c r="C713" s="9"/>
     </row>
-    <row r="714">
-      <c r="A714" s="9"/>
-      <c r="B714" s="9"/>
+    <row r="714" spans="3:3">
       <c r="C714" s="9"/>
     </row>
-    <row r="715">
-      <c r="A715" s="9"/>
-      <c r="B715" s="9"/>
+    <row r="715" spans="3:3">
       <c r="C715" s="9"/>
     </row>
-    <row r="716">
-      <c r="A716" s="9"/>
-      <c r="B716" s="9"/>
+    <row r="716" spans="3:3">
       <c r="C716" s="9"/>
     </row>
-    <row r="717">
-      <c r="A717" s="9"/>
-      <c r="B717" s="9"/>
+    <row r="717" spans="3:3">
       <c r="C717" s="9"/>
     </row>
-    <row r="718">
-      <c r="A718" s="9"/>
-      <c r="B718" s="9"/>
+    <row r="718" spans="3:3">
       <c r="C718" s="9"/>
     </row>
-    <row r="719">
-      <c r="A719" s="9"/>
-      <c r="B719" s="9"/>
+    <row r="719" spans="3:3">
       <c r="C719" s="9"/>
     </row>
-    <row r="720">
-      <c r="A720" s="9"/>
-      <c r="B720" s="9"/>
+    <row r="720" spans="3:3">
       <c r="C720" s="9"/>
     </row>
-    <row r="721">
-      <c r="A721" s="9"/>
-      <c r="B721" s="9"/>
+    <row r="721" spans="3:3">
       <c r="C721" s="9"/>
     </row>
-    <row r="722">
-      <c r="A722" s="9"/>
-      <c r="B722" s="9"/>
+    <row r="722" spans="3:3">
       <c r="C722" s="9"/>
     </row>
-    <row r="723">
-      <c r="A723" s="9"/>
-      <c r="B723" s="9"/>
+    <row r="723" spans="3:3">
       <c r="C723" s="9"/>
     </row>
-    <row r="724">
-      <c r="A724" s="9"/>
-      <c r="B724" s="9"/>
+    <row r="724" spans="3:3">
       <c r="C724" s="9"/>
     </row>
-    <row r="725">
-      <c r="A725" s="9"/>
-      <c r="B725" s="9"/>
+    <row r="725" spans="3:3">
       <c r="C725" s="9"/>
     </row>
-    <row r="726">
-      <c r="A726" s="9"/>
-      <c r="B726" s="9"/>
+    <row r="726" spans="3:3">
       <c r="C726" s="9"/>
     </row>
-    <row r="727">
-      <c r="A727" s="9"/>
-      <c r="B727" s="9"/>
+    <row r="727" spans="3:3">
       <c r="C727" s="9"/>
     </row>
-    <row r="728">
-      <c r="A728" s="9"/>
-      <c r="B728" s="9"/>
+    <row r="728" spans="3:3">
       <c r="C728" s="9"/>
     </row>
-    <row r="729">
-      <c r="A729" s="9"/>
-      <c r="B729" s="9"/>
+    <row r="729" spans="3:3">
       <c r="C729" s="9"/>
     </row>
-    <row r="730">
-      <c r="A730" s="9"/>
-      <c r="B730" s="9"/>
+    <row r="730" spans="3:3">
       <c r="C730" s="9"/>
     </row>
-    <row r="731">
-      <c r="A731" s="9"/>
-      <c r="B731" s="9"/>
+    <row r="731" spans="3:3">
       <c r="C731" s="9"/>
     </row>
-    <row r="732">
-      <c r="A732" s="9"/>
-      <c r="B732" s="9"/>
+    <row r="732" spans="3:3">
       <c r="C732" s="9"/>
     </row>
-    <row r="733">
-      <c r="A733" s="9"/>
-      <c r="B733" s="9"/>
+    <row r="733" spans="3:3">
       <c r="C733" s="9"/>
     </row>
-    <row r="734">
-      <c r="A734" s="9"/>
-      <c r="B734" s="9"/>
+    <row r="734" spans="3:3">
       <c r="C734" s="9"/>
     </row>
-    <row r="735">
-      <c r="A735" s="9"/>
-      <c r="B735" s="9"/>
+    <row r="735" spans="3:3">
       <c r="C735" s="9"/>
     </row>
-    <row r="736">
-      <c r="A736" s="9"/>
-      <c r="B736" s="9"/>
+    <row r="736" spans="3:3">
       <c r="C736" s="9"/>
     </row>
-    <row r="737">
-      <c r="A737" s="9"/>
-      <c r="B737" s="9"/>
+    <row r="737" spans="3:3">
       <c r="C737" s="9"/>
     </row>
-    <row r="738">
-      <c r="A738" s="9"/>
-      <c r="B738" s="9"/>
+    <row r="738" spans="3:3">
       <c r="C738" s="9"/>
     </row>
-    <row r="739">
-      <c r="A739" s="9"/>
-      <c r="B739" s="9"/>
+    <row r="739" spans="3:3">
       <c r="C739" s="9"/>
     </row>
-    <row r="740">
-      <c r="A740" s="9"/>
-      <c r="B740" s="9"/>
+    <row r="740" spans="3:3">
       <c r="C740" s="9"/>
     </row>
-    <row r="741">
-      <c r="A741" s="9"/>
-      <c r="B741" s="9"/>
+    <row r="741" spans="3:3">
       <c r="C741" s="9"/>
     </row>
-    <row r="742">
-      <c r="A742" s="9"/>
-      <c r="B742" s="9"/>
+    <row r="742" spans="3:3">
       <c r="C742" s="9"/>
     </row>
-    <row r="743">
-      <c r="A743" s="9"/>
-      <c r="B743" s="9"/>
+    <row r="743" spans="3:3">
       <c r="C743" s="9"/>
     </row>
-    <row r="744">
-      <c r="A744" s="9"/>
-      <c r="B744" s="9"/>
+    <row r="744" spans="3:3">
       <c r="C744" s="9"/>
     </row>
-    <row r="745">
-      <c r="A745" s="9"/>
-      <c r="B745" s="9"/>
+    <row r="745" spans="3:3">
       <c r="C745" s="9"/>
     </row>
-    <row r="746">
-      <c r="A746" s="9"/>
-      <c r="B746" s="9"/>
+    <row r="746" spans="3:3">
       <c r="C746" s="9"/>
     </row>
-    <row r="747">
-      <c r="A747" s="9"/>
-      <c r="B747" s="9"/>
+    <row r="747" spans="3:3">
       <c r="C747" s="9"/>
     </row>
-    <row r="748">
-      <c r="A748" s="9"/>
-      <c r="B748" s="9"/>
+    <row r="748" spans="3:3">
       <c r="C748" s="9"/>
     </row>
-    <row r="749">
-      <c r="A749" s="9"/>
-      <c r="B749" s="9"/>
+    <row r="749" spans="3:3">
       <c r="C749" s="9"/>
     </row>
-    <row r="750">
-      <c r="A750" s="9"/>
-      <c r="B750" s="9"/>
+    <row r="750" spans="3:3">
       <c r="C750" s="9"/>
     </row>
-    <row r="751">
-      <c r="A751" s="9"/>
-      <c r="B751" s="9"/>
+    <row r="751" spans="3:3">
       <c r="C751" s="9"/>
     </row>
-    <row r="752">
-      <c r="A752" s="9"/>
-      <c r="B752" s="9"/>
+    <row r="752" spans="3:3">
       <c r="C752" s="9"/>
     </row>
-    <row r="753">
-      <c r="A753" s="9"/>
-      <c r="B753" s="9"/>
+    <row r="753" spans="3:3">
       <c r="C753" s="9"/>
     </row>
-    <row r="754">
-      <c r="A754" s="9"/>
-      <c r="B754" s="9"/>
+    <row r="754" spans="3:3">
       <c r="C754" s="9"/>
     </row>
-    <row r="755">
-      <c r="A755" s="9"/>
-      <c r="B755" s="9"/>
+    <row r="755" spans="3:3">
       <c r="C755" s="9"/>
     </row>
-    <row r="756">
-      <c r="A756" s="9"/>
-      <c r="B756" s="9"/>
+    <row r="756" spans="3:3">
       <c r="C756" s="9"/>
     </row>
-    <row r="757">
-      <c r="A757" s="9"/>
-      <c r="B757" s="9"/>
+    <row r="757" spans="3:3">
       <c r="C757" s="9"/>
     </row>
-    <row r="758">
-      <c r="A758" s="9"/>
-      <c r="B758" s="9"/>
+    <row r="758" spans="3:3">
       <c r="C758" s="9"/>
     </row>
-    <row r="759">
-      <c r="A759" s="9"/>
-      <c r="B759" s="9"/>
+    <row r="759" spans="3:3">
       <c r="C759" s="9"/>
     </row>
-    <row r="760">
-      <c r="A760" s="9"/>
-      <c r="B760" s="9"/>
+    <row r="760" spans="3:3">
       <c r="C760" s="9"/>
     </row>
-    <row r="761">
-      <c r="A761" s="9"/>
-      <c r="B761" s="9"/>
+    <row r="761" spans="3:3">
       <c r="C761" s="9"/>
     </row>
-    <row r="762">
-      <c r="A762" s="9"/>
-      <c r="B762" s="9"/>
+    <row r="762" spans="3:3">
       <c r="C762" s="9"/>
     </row>
-    <row r="763">
-      <c r="A763" s="9"/>
-      <c r="B763" s="9"/>
+    <row r="763" spans="3:3">
       <c r="C763" s="9"/>
     </row>
-    <row r="764">
-      <c r="A764" s="9"/>
-      <c r="B764" s="9"/>
+    <row r="764" spans="3:3">
       <c r="C764" s="9"/>
     </row>
-    <row r="765">
-      <c r="A765" s="9"/>
-      <c r="B765" s="9"/>
+    <row r="765" spans="3:3">
       <c r="C765" s="9"/>
     </row>
-    <row r="766">
-      <c r="A766" s="9"/>
-      <c r="B766" s="9"/>
+    <row r="766" spans="3:3">
       <c r="C766" s="9"/>
     </row>
-    <row r="767">
-      <c r="A767" s="9"/>
-      <c r="B767" s="9"/>
+    <row r="767" spans="3:3">
       <c r="C767" s="9"/>
     </row>
-    <row r="768">
-      <c r="A768" s="9"/>
-      <c r="B768" s="9"/>
+    <row r="768" spans="3:3">
       <c r="C768" s="9"/>
     </row>
-    <row r="769">
-      <c r="A769" s="9"/>
-      <c r="B769" s="9"/>
+    <row r="769" spans="3:3">
       <c r="C769" s="9"/>
     </row>
-    <row r="770">
-      <c r="A770" s="9"/>
-      <c r="B770" s="9"/>
+    <row r="770" spans="3:3">
       <c r="C770" s="9"/>
     </row>
-    <row r="771">
-      <c r="A771" s="9"/>
-      <c r="B771" s="9"/>
+    <row r="771" spans="3:3">
       <c r="C771" s="9"/>
     </row>
-    <row r="772">
-      <c r="A772" s="9"/>
-      <c r="B772" s="9"/>
+    <row r="772" spans="3:3">
       <c r="C772" s="9"/>
     </row>
-    <row r="773">
-      <c r="A773" s="9"/>
-      <c r="B773" s="9"/>
+    <row r="773" spans="3:3">
       <c r="C773" s="9"/>
     </row>
-    <row r="774">
-      <c r="A774" s="9"/>
-      <c r="B774" s="9"/>
+    <row r="774" spans="3:3">
       <c r="C774" s="9"/>
     </row>
-    <row r="775">
-      <c r="A775" s="9"/>
-      <c r="B775" s="9"/>
+    <row r="775" spans="3:3">
       <c r="C775" s="9"/>
     </row>
-    <row r="776">
-      <c r="A776" s="9"/>
-      <c r="B776" s="9"/>
+    <row r="776" spans="3:3">
       <c r="C776" s="9"/>
     </row>
-    <row r="777">
-      <c r="A777" s="9"/>
-      <c r="B777" s="9"/>
+    <row r="777" spans="3:3">
       <c r="C777" s="9"/>
     </row>
-    <row r="778">
-      <c r="A778" s="9"/>
-      <c r="B778" s="9"/>
+    <row r="778" spans="3:3">
       <c r="C778" s="9"/>
     </row>
-    <row r="779">
-      <c r="A779" s="9"/>
-      <c r="B779" s="9"/>
+    <row r="779" spans="3:3">
       <c r="C779" s="9"/>
     </row>
-    <row r="780">
-      <c r="A780" s="9"/>
-      <c r="B780" s="9"/>
+    <row r="780" spans="3:3">
       <c r="C780" s="9"/>
     </row>
-    <row r="781">
-      <c r="A781" s="9"/>
-      <c r="B781" s="9"/>
+    <row r="781" spans="3:3">
       <c r="C781" s="9"/>
     </row>
-    <row r="782">
-      <c r="A782" s="9"/>
-      <c r="B782" s="9"/>
+    <row r="782" spans="3:3">
       <c r="C782" s="9"/>
     </row>
-    <row r="783">
-      <c r="A783" s="9"/>
-      <c r="B783" s="9"/>
+    <row r="783" spans="3:3">
       <c r="C783" s="9"/>
     </row>
-    <row r="784">
-      <c r="A784" s="9"/>
-      <c r="B784" s="9"/>
+    <row r="784" spans="3:3">
       <c r="C784" s="9"/>
     </row>
-    <row r="785">
-      <c r="A785" s="9"/>
-      <c r="B785" s="9"/>
+    <row r="785" spans="3:3">
       <c r="C785" s="9"/>
     </row>
-    <row r="786">
-      <c r="A786" s="9"/>
-      <c r="B786" s="9"/>
+    <row r="786" spans="3:3">
       <c r="C786" s="9"/>
     </row>
-    <row r="787">
-      <c r="A787" s="9"/>
-      <c r="B787" s="9"/>
+    <row r="787" spans="3:3">
       <c r="C787" s="9"/>
     </row>
-    <row r="788">
-      <c r="A788" s="9"/>
-      <c r="B788" s="9"/>
+    <row r="788" spans="3:3">
       <c r="C788" s="9"/>
     </row>
-    <row r="789">
-      <c r="A789" s="9"/>
-      <c r="B789" s="9"/>
+    <row r="789" spans="3:3">
       <c r="C789" s="9"/>
     </row>
-    <row r="790">
-      <c r="A790" s="9"/>
-      <c r="B790" s="9"/>
+    <row r="790" spans="3:3">
       <c r="C790" s="9"/>
     </row>
-    <row r="791">
-      <c r="A791" s="9"/>
-      <c r="B791" s="9"/>
+    <row r="791" spans="3:3">
       <c r="C791" s="9"/>
     </row>
-    <row r="792">
-      <c r="A792" s="9"/>
-      <c r="B792" s="9"/>
+    <row r="792" spans="3:3">
       <c r="C792" s="9"/>
     </row>
-    <row r="793">
-      <c r="A793" s="9"/>
-      <c r="B793" s="9"/>
+    <row r="793" spans="3:3">
       <c r="C793" s="9"/>
     </row>
-    <row r="794">
-      <c r="A794" s="9"/>
-      <c r="B794" s="9"/>
+    <row r="794" spans="3:3">
       <c r="C794" s="9"/>
     </row>
-    <row r="795">
-      <c r="A795" s="9"/>
-      <c r="B795" s="9"/>
+    <row r="795" spans="3:3">
       <c r="C795" s="9"/>
     </row>
-    <row r="796">
-      <c r="A796" s="9"/>
-      <c r="B796" s="9"/>
+    <row r="796" spans="3:3">
       <c r="C796" s="9"/>
     </row>
-    <row r="797">
-      <c r="A797" s="9"/>
-      <c r="B797" s="9"/>
+    <row r="797" spans="3:3">
       <c r="C797" s="9"/>
     </row>
-    <row r="798">
-      <c r="A798" s="9"/>
-      <c r="B798" s="9"/>
+    <row r="798" spans="3:3">
       <c r="C798" s="9"/>
     </row>
-    <row r="799">
-      <c r="A799" s="9"/>
-      <c r="B799" s="9"/>
+    <row r="799" spans="3:3">
       <c r="C799" s="9"/>
     </row>
-    <row r="800">
-      <c r="A800" s="9"/>
-      <c r="B800" s="9"/>
+    <row r="800" spans="3:3">
       <c r="C800" s="9"/>
     </row>
-    <row r="801">
-      <c r="A801" s="9"/>
-      <c r="B801" s="9"/>
+    <row r="801" spans="3:3">
       <c r="C801" s="9"/>
     </row>
-    <row r="802">
-      <c r="A802" s="9"/>
-      <c r="B802" s="9"/>
+    <row r="802" spans="3:3">
       <c r="C802" s="9"/>
     </row>
-    <row r="803">
-      <c r="A803" s="9"/>
-      <c r="B803" s="9"/>
+    <row r="803" spans="3:3">
       <c r="C803" s="9"/>
     </row>
-    <row r="804">
-      <c r="A804" s="9"/>
-      <c r="B804" s="9"/>
+    <row r="804" spans="3:3">
       <c r="C804" s="9"/>
     </row>
-    <row r="805">
-      <c r="A805" s="9"/>
-      <c r="B805" s="9"/>
+    <row r="805" spans="3:3">
       <c r="C805" s="9"/>
     </row>
-    <row r="806">
-      <c r="A806" s="9"/>
-      <c r="B806" s="9"/>
+    <row r="806" spans="3:3">
       <c r="C806" s="9"/>
     </row>
-    <row r="807">
-      <c r="A807" s="9"/>
-      <c r="B807" s="9"/>
+    <row r="807" spans="3:3">
       <c r="C807" s="9"/>
     </row>
-    <row r="808">
-      <c r="A808" s="9"/>
-      <c r="B808" s="9"/>
+    <row r="808" spans="3:3">
       <c r="C808" s="9"/>
     </row>
-    <row r="809">
-      <c r="A809" s="9"/>
-      <c r="B809" s="9"/>
+    <row r="809" spans="3:3">
       <c r="C809" s="9"/>
     </row>
-    <row r="810">
-      <c r="A810" s="9"/>
-      <c r="B810" s="9"/>
+    <row r="810" spans="3:3">
       <c r="C810" s="9"/>
     </row>
-    <row r="811">
-      <c r="A811" s="9"/>
-      <c r="B811" s="9"/>
+    <row r="811" spans="3:3">
       <c r="C811" s="9"/>
     </row>
-    <row r="812">
-      <c r="A812" s="9"/>
-      <c r="B812" s="9"/>
+    <row r="812" spans="3:3">
       <c r="C812" s="9"/>
     </row>
-    <row r="813">
-      <c r="A813" s="9"/>
-      <c r="B813" s="9"/>
+    <row r="813" spans="3:3">
       <c r="C813" s="9"/>
     </row>
-    <row r="814">
-      <c r="A814" s="9"/>
-      <c r="B814" s="9"/>
+    <row r="814" spans="3:3">
       <c r="C814" s="9"/>
     </row>
-    <row r="815">
-      <c r="A815" s="9"/>
-      <c r="B815" s="9"/>
+    <row r="815" spans="3:3">
       <c r="C815" s="9"/>
     </row>
-    <row r="816">
-      <c r="A816" s="9"/>
-      <c r="B816" s="9"/>
+    <row r="816" spans="3:3">
       <c r="C816" s="9"/>
     </row>
-    <row r="817">
-      <c r="A817" s="9"/>
-      <c r="B817" s="9"/>
+    <row r="817" spans="3:3">
       <c r="C817" s="9"/>
     </row>
-    <row r="818">
-      <c r="A818" s="9"/>
-      <c r="B818" s="9"/>
+    <row r="818" spans="3:3">
       <c r="C818" s="9"/>
     </row>
-    <row r="819">
-      <c r="A819" s="9"/>
-      <c r="B819" s="9"/>
+    <row r="819" spans="3:3">
       <c r="C819" s="9"/>
     </row>
-    <row r="820">
-      <c r="A820" s="9"/>
-      <c r="B820" s="9"/>
+    <row r="820" spans="3:3">
       <c r="C820" s="9"/>
     </row>
-    <row r="821">
-      <c r="A821" s="9"/>
-      <c r="B821" s="9"/>
+    <row r="821" spans="3:3">
       <c r="C821" s="9"/>
     </row>
-    <row r="822">
-      <c r="A822" s="9"/>
-      <c r="B822" s="9"/>
+    <row r="822" spans="3:3">
       <c r="C822" s="9"/>
     </row>
-    <row r="823">
-      <c r="A823" s="9"/>
-      <c r="B823" s="9"/>
+    <row r="823" spans="3:3">
       <c r="C823" s="9"/>
     </row>
-    <row r="824">
-      <c r="A824" s="9"/>
-      <c r="B824" s="9"/>
+    <row r="824" spans="3:3">
       <c r="C824" s="9"/>
     </row>
-    <row r="825">
-      <c r="A825" s="9"/>
-      <c r="B825" s="9"/>
+    <row r="825" spans="3:3">
       <c r="C825" s="9"/>
     </row>
-    <row r="826">
-      <c r="A826" s="9"/>
-      <c r="B826" s="9"/>
+    <row r="826" spans="3:3">
       <c r="C826" s="9"/>
     </row>
-    <row r="827">
-      <c r="A827" s="9"/>
-      <c r="B827" s="9"/>
+    <row r="827" spans="3:3">
       <c r="C827" s="9"/>
     </row>
-    <row r="828">
-      <c r="A828" s="9"/>
-      <c r="B828" s="9"/>
+    <row r="828" spans="3:3">
       <c r="C828" s="9"/>
     </row>
-    <row r="829">
-      <c r="A829" s="9"/>
-      <c r="B829" s="9"/>
+    <row r="829" spans="3:3">
       <c r="C829" s="9"/>
     </row>
-    <row r="830">
-      <c r="A830" s="9"/>
-      <c r="B830" s="9"/>
+    <row r="830" spans="3:3">
       <c r="C830" s="9"/>
     </row>
-    <row r="831">
-      <c r="A831" s="9"/>
-      <c r="B831" s="9"/>
+    <row r="831" spans="3:3">
       <c r="C831" s="9"/>
     </row>
-    <row r="832">
-      <c r="A832" s="9"/>
-      <c r="B832" s="9"/>
+    <row r="832" spans="3:3">
       <c r="C832" s="9"/>
     </row>
-    <row r="833">
-      <c r="A833" s="9"/>
-      <c r="B833" s="9"/>
+    <row r="833" spans="3:3">
       <c r="C833" s="9"/>
     </row>
-    <row r="834">
-      <c r="A834" s="9"/>
-      <c r="B834" s="9"/>
+    <row r="834" spans="3:3">
       <c r="C834" s="9"/>
     </row>
-    <row r="835">
-      <c r="A835" s="9"/>
-      <c r="B835" s="9"/>
+    <row r="835" spans="3:3">
       <c r="C835" s="9"/>
     </row>
-    <row r="836">
-      <c r="A836" s="9"/>
-      <c r="B836" s="9"/>
+    <row r="836" spans="3:3">
       <c r="C836" s="9"/>
     </row>
-    <row r="837">
-      <c r="A837" s="9"/>
-      <c r="B837" s="9"/>
+    <row r="837" spans="3:3">
       <c r="C837" s="9"/>
     </row>
-    <row r="838">
-      <c r="A838" s="9"/>
-      <c r="B838" s="9"/>
+    <row r="838" spans="3:3">
       <c r="C838" s="9"/>
     </row>
-    <row r="839">
-      <c r="A839" s="9"/>
-      <c r="B839" s="9"/>
+    <row r="839" spans="3:3">
       <c r="C839" s="9"/>
     </row>
-    <row r="840">
-      <c r="A840" s="9"/>
-      <c r="B840" s="9"/>
+    <row r="840" spans="3:3">
       <c r="C840" s="9"/>
     </row>
-    <row r="841">
-      <c r="A841" s="9"/>
-      <c r="B841" s="9"/>
+    <row r="841" spans="3:3">
       <c r="C841" s="9"/>
     </row>
-    <row r="842">
-      <c r="A842" s="9"/>
-      <c r="B842" s="9"/>
+    <row r="842" spans="3:3">
       <c r="C842" s="9"/>
     </row>
-    <row r="843">
-      <c r="A843" s="9"/>
-      <c r="B843" s="9"/>
+    <row r="843" spans="3:3">
       <c r="C843" s="9"/>
     </row>
-    <row r="844">
-      <c r="A844" s="9"/>
-      <c r="B844" s="9"/>
+    <row r="844" spans="3:3">
       <c r="C844" s="9"/>
     </row>
-    <row r="845">
-      <c r="A845" s="9"/>
-      <c r="B845" s="9"/>
+    <row r="845" spans="3:3">
       <c r="C845" s="9"/>
     </row>
-    <row r="846">
-      <c r="A846" s="9"/>
-      <c r="B846" s="9"/>
+    <row r="846" spans="3:3">
       <c r="C846" s="9"/>
     </row>
-    <row r="847">
-      <c r="A847" s="9"/>
-      <c r="B847" s="9"/>
+    <row r="847" spans="3:3">
       <c r="C847" s="9"/>
     </row>
-    <row r="848">
-      <c r="A848" s="9"/>
-      <c r="B848" s="9"/>
+    <row r="848" spans="3:3">
       <c r="C848" s="9"/>
     </row>
-    <row r="849">
-      <c r="A849" s="9"/>
-      <c r="B849" s="9"/>
+    <row r="849" spans="3:3">
       <c r="C849" s="9"/>
     </row>
-    <row r="850">
-      <c r="A850" s="9"/>
-      <c r="B850" s="9"/>
+    <row r="850" spans="3:3">
       <c r="C850" s="9"/>
     </row>
-    <row r="851">
-      <c r="A851" s="9"/>
-      <c r="B851" s="9"/>
+    <row r="851" spans="3:3">
       <c r="C851" s="9"/>
     </row>
-    <row r="852">
-      <c r="A852" s="9"/>
-      <c r="B852" s="9"/>
+    <row r="852" spans="3:3">
       <c r="C852" s="9"/>
     </row>
-    <row r="853">
-      <c r="A853" s="9"/>
-      <c r="B853" s="9"/>
+    <row r="853" spans="3:3">
       <c r="C853" s="9"/>
     </row>
-    <row r="854">
-      <c r="A854" s="9"/>
-      <c r="B854" s="9"/>
+    <row r="854" spans="3:3">
       <c r="C854" s="9"/>
     </row>
-    <row r="855">
-      <c r="A855" s="9"/>
-      <c r="B855" s="9"/>
+    <row r="855" spans="3:3">
       <c r="C855" s="9"/>
     </row>
-    <row r="856">
-      <c r="A856" s="9"/>
-      <c r="B856" s="9"/>
+    <row r="856" spans="3:3">
       <c r="C856" s="9"/>
     </row>
-    <row r="857">
-      <c r="A857" s="9"/>
-      <c r="B857" s="9"/>
+    <row r="857" spans="3:3">
       <c r="C857" s="9"/>
     </row>
-    <row r="858">
-      <c r="A858" s="9"/>
-      <c r="B858" s="9"/>
+    <row r="858" spans="3:3">
       <c r="C858" s="9"/>
     </row>
-    <row r="859">
-      <c r="A859" s="9"/>
-      <c r="B859" s="9"/>
+    <row r="859" spans="3:3">
       <c r="C859" s="9"/>
     </row>
-    <row r="860">
-      <c r="A860" s="9"/>
-      <c r="B860" s="9"/>
+    <row r="860" spans="3:3">
       <c r="C860" s="9"/>
     </row>
-    <row r="861">
-      <c r="A861" s="9"/>
-      <c r="B861" s="9"/>
+    <row r="861" spans="3:3">
       <c r="C861" s="9"/>
     </row>
-    <row r="862">
-      <c r="A862" s="9"/>
-      <c r="B862" s="9"/>
+    <row r="862" spans="3:3">
       <c r="C862" s="9"/>
     </row>
-    <row r="863">
-      <c r="A863" s="9"/>
-      <c r="B863" s="9"/>
+    <row r="863" spans="3:3">
       <c r="C863" s="9"/>
     </row>
-    <row r="864">
-      <c r="A864" s="9"/>
-      <c r="B864" s="9"/>
+    <row r="864" spans="3:3">
       <c r="C864" s="9"/>
     </row>
-    <row r="865">
-      <c r="A865" s="9"/>
-      <c r="B865" s="9"/>
+    <row r="865" spans="3:3">
       <c r="C865" s="9"/>
     </row>
-    <row r="866">
-      <c r="A866" s="9"/>
-      <c r="B866" s="9"/>
+    <row r="866" spans="3:3">
       <c r="C866" s="9"/>
     </row>
-    <row r="867">
-      <c r="A867" s="9"/>
-      <c r="B867" s="9"/>
+    <row r="867" spans="3:3">
       <c r="C867" s="9"/>
     </row>
-    <row r="868">
-      <c r="A868" s="9"/>
-      <c r="B868" s="9"/>
+    <row r="868" spans="3:3">
       <c r="C868" s="9"/>
     </row>
-    <row r="869">
-      <c r="A869" s="9"/>
-      <c r="B869" s="9"/>
+    <row r="869" spans="3:3">
       <c r="C869" s="9"/>
     </row>
-    <row r="870">
-      <c r="A870" s="9"/>
-      <c r="B870" s="9"/>
+    <row r="870" spans="3:3">
       <c r="C870" s="9"/>
     </row>
-    <row r="871">
-      <c r="A871" s="9"/>
-      <c r="B871" s="9"/>
+    <row r="871" spans="3:3">
       <c r="C871" s="9"/>
     </row>
-    <row r="872">
-      <c r="A872" s="9"/>
-      <c r="B872" s="9"/>
+    <row r="872" spans="3:3">
       <c r="C872" s="9"/>
     </row>
-    <row r="873">
-      <c r="A873" s="9"/>
-      <c r="B873" s="9"/>
+    <row r="873" spans="3:3">
       <c r="C873" s="9"/>
     </row>
-    <row r="874">
-      <c r="A874" s="9"/>
-      <c r="B874" s="9"/>
+    <row r="874" spans="3:3">
       <c r="C874" s="9"/>
     </row>
-    <row r="875">
-      <c r="A875" s="9"/>
-      <c r="B875" s="9"/>
+    <row r="875" spans="3:3">
       <c r="C875" s="9"/>
     </row>
-    <row r="876">
-      <c r="A876" s="9"/>
-      <c r="B876" s="9"/>
+    <row r="876" spans="3:3">
       <c r="C876" s="9"/>
     </row>
-    <row r="877">
-      <c r="A877" s="9"/>
-      <c r="B877" s="9"/>
+    <row r="877" spans="3:3">
       <c r="C877" s="9"/>
     </row>
-    <row r="878">
-      <c r="A878" s="9"/>
-      <c r="B878" s="9"/>
+    <row r="878" spans="3:3">
       <c r="C878" s="9"/>
     </row>
-    <row r="879">
-      <c r="A879" s="9"/>
-      <c r="B879" s="9"/>
+    <row r="879" spans="3:3">
       <c r="C879" s="9"/>
     </row>
-    <row r="880">
-      <c r="A880" s="9"/>
-      <c r="B880" s="9"/>
+    <row r="880" spans="3:3">
       <c r="C880" s="9"/>
     </row>
-    <row r="881">
-      <c r="A881" s="9"/>
-      <c r="B881" s="9"/>
+    <row r="881" spans="3:3">
       <c r="C881" s="9"/>
     </row>
-    <row r="882">
-      <c r="A882" s="9"/>
-      <c r="B882" s="9"/>
+    <row r="882" spans="3:3">
       <c r="C882" s="9"/>
     </row>
-    <row r="883">
-      <c r="A883" s="9"/>
-      <c r="B883" s="9"/>
+    <row r="883" spans="3:3">
       <c r="C883" s="9"/>
     </row>
-    <row r="884">
-      <c r="A884" s="9"/>
-      <c r="B884" s="9"/>
+    <row r="884" spans="3:3">
       <c r="C884" s="9"/>
     </row>
-    <row r="885">
-      <c r="A885" s="9"/>
-      <c r="B885" s="9"/>
+    <row r="885" spans="3:3">
       <c r="C885" s="9"/>
     </row>
-    <row r="886">
-      <c r="A886" s="9"/>
-      <c r="B886" s="9"/>
+    <row r="886" spans="3:3">
       <c r="C886" s="9"/>
     </row>
-    <row r="887">
-      <c r="A887" s="9"/>
-      <c r="B887" s="9"/>
+    <row r="887" spans="3:3">
       <c r="C887" s="9"/>
     </row>
-    <row r="888">
-      <c r="A888" s="9"/>
-      <c r="B888" s="9"/>
+    <row r="888" spans="3:3">
       <c r="C888" s="9"/>
     </row>
-    <row r="889">
-      <c r="A889" s="9"/>
-      <c r="B889" s="9"/>
+    <row r="889" spans="3:3">
       <c r="C889" s="9"/>
     </row>
-    <row r="890">
-      <c r="A890" s="9"/>
-      <c r="B890" s="9"/>
+    <row r="890" spans="3:3">
       <c r="C890" s="9"/>
     </row>
-    <row r="891">
-      <c r="A891" s="9"/>
-      <c r="B891" s="9"/>
+    <row r="891" spans="3:3">
       <c r="C891" s="9"/>
     </row>
-    <row r="892">
-      <c r="A892" s="9"/>
-      <c r="B892" s="9"/>
+    <row r="892" spans="3:3">
       <c r="C892" s="9"/>
     </row>
-    <row r="893">
-      <c r="A893" s="9"/>
-      <c r="B893" s="9"/>
+    <row r="893" spans="3:3">
       <c r="C893" s="9"/>
     </row>
-    <row r="894">
-      <c r="A894" s="9"/>
-      <c r="B894" s="9"/>
+    <row r="894" spans="3:3">
       <c r="C894" s="9"/>
     </row>
-    <row r="895">
-      <c r="A895" s="9"/>
-      <c r="B895" s="9"/>
+    <row r="895" spans="3:3">
       <c r="C895" s="9"/>
     </row>
-    <row r="896">
-      <c r="A896" s="9"/>
-      <c r="B896" s="9"/>
+    <row r="896" spans="3:3">
       <c r="C896" s="9"/>
     </row>
-    <row r="897">
-      <c r="A897" s="9"/>
-      <c r="B897" s="9"/>
+    <row r="897" spans="3:3">
       <c r="C897" s="9"/>
     </row>
-    <row r="898">
-      <c r="A898" s="9"/>
-      <c r="B898" s="9"/>
+    <row r="898" spans="3:3">
       <c r="C898" s="9"/>
     </row>
-    <row r="899">
-      <c r="A899" s="9"/>
-      <c r="B899" s="9"/>
+    <row r="899" spans="3:3">
       <c r="C899" s="9"/>
     </row>
-    <row r="900">
-      <c r="A900" s="9"/>
-      <c r="B900" s="9"/>
+    <row r="900" spans="3:3">
       <c r="C900" s="9"/>
     </row>
-    <row r="901">
-      <c r="A901" s="9"/>
-      <c r="B901" s="9"/>
+    <row r="901" spans="3:3">
       <c r="C901" s="9"/>
     </row>
-    <row r="902">
-      <c r="A902" s="9"/>
-      <c r="B902" s="9"/>
+    <row r="902" spans="3:3">
       <c r="C902" s="9"/>
     </row>
-    <row r="903">
-      <c r="A903" s="9"/>
-      <c r="B903" s="9"/>
+    <row r="903" spans="3:3">
       <c r="C903" s="9"/>
     </row>
-    <row r="904">
-      <c r="A904" s="9"/>
-      <c r="B904" s="9"/>
+    <row r="904" spans="3:3">
       <c r="C904" s="9"/>
     </row>
-    <row r="905">
-      <c r="A905" s="9"/>
-      <c r="B905" s="9"/>
+    <row r="905" spans="3:3">
       <c r="C905" s="9"/>
     </row>
-    <row r="906">
-      <c r="A906" s="9"/>
-      <c r="B906" s="9"/>
+    <row r="906" spans="3:3">
       <c r="C906" s="9"/>
     </row>
-    <row r="907">
-      <c r="A907" s="9"/>
-      <c r="B907" s="9"/>
+    <row r="907" spans="3:3">
       <c r="C907" s="9"/>
     </row>
-    <row r="908">
-      <c r="A908" s="9"/>
-      <c r="B908" s="9"/>
+    <row r="908" spans="3:3">
       <c r="C908" s="9"/>
     </row>
-    <row r="909">
-      <c r="A909" s="9"/>
-      <c r="B909" s="9"/>
+    <row r="909" spans="3:3">
       <c r="C909" s="9"/>
     </row>
-    <row r="910">
-      <c r="A910" s="9"/>
-      <c r="B910" s="9"/>
+    <row r="910" spans="3:3">
       <c r="C910" s="9"/>
     </row>
-    <row r="911">
-      <c r="A911" s="9"/>
-      <c r="B911" s="9"/>
+    <row r="911" spans="3:3">
       <c r="C911" s="9"/>
     </row>
-    <row r="912">
-      <c r="A912" s="9"/>
-      <c r="B912" s="9"/>
+    <row r="912" spans="3:3">
       <c r="C912" s="9"/>
     </row>
-    <row r="913">
-      <c r="A913" s="9"/>
-      <c r="B913" s="9"/>
+    <row r="913" spans="3:3">
       <c r="C913" s="9"/>
     </row>
-    <row r="914">
-      <c r="A914" s="9"/>
-      <c r="B914" s="9"/>
+    <row r="914" spans="3:3">
       <c r="C914" s="9"/>
     </row>
-    <row r="915">
-      <c r="A915" s="9"/>
-      <c r="B915" s="9"/>
+    <row r="915" spans="3:3">
       <c r="C915" s="9"/>
     </row>
-    <row r="916">
-      <c r="A916" s="9"/>
-      <c r="B916" s="9"/>
+    <row r="916" spans="3:3">
       <c r="C916" s="9"/>
     </row>
-    <row r="917">
-      <c r="A917" s="9"/>
-      <c r="B917" s="9"/>
+    <row r="917" spans="3:3">
       <c r="C917" s="9"/>
     </row>
-    <row r="918">
-      <c r="A918" s="9"/>
-      <c r="B918" s="9"/>
+    <row r="918" spans="3:3">
       <c r="C918" s="9"/>
     </row>
-    <row r="919">
-      <c r="A919" s="9"/>
-      <c r="B919" s="9"/>
+    <row r="919" spans="3:3">
       <c r="C919" s="9"/>
     </row>
-    <row r="920">
-      <c r="A920" s="9"/>
-      <c r="B920" s="9"/>
+    <row r="920" spans="3:3">
       <c r="C920" s="9"/>
     </row>
-    <row r="921">
-      <c r="A921" s="9"/>
-      <c r="B921" s="9"/>
+    <row r="921" spans="3:3">
       <c r="C921" s="9"/>
     </row>
-    <row r="922">
-      <c r="A922" s="9"/>
-      <c r="B922" s="9"/>
+    <row r="922" spans="3:3">
       <c r="C922" s="9"/>
     </row>
-    <row r="923">
-      <c r="A923" s="9"/>
-      <c r="B923" s="9"/>
+    <row r="923" spans="3:3">
       <c r="C923" s="9"/>
     </row>
-    <row r="924">
-      <c r="A924" s="9"/>
-      <c r="B924" s="9"/>
+    <row r="924" spans="3:3">
       <c r="C924" s="9"/>
     </row>
-    <row r="925">
-      <c r="A925" s="9"/>
-      <c r="B925" s="9"/>
+    <row r="925" spans="3:3">
       <c r="C925" s="9"/>
     </row>
-    <row r="926">
-      <c r="A926" s="9"/>
-      <c r="B926" s="9"/>
+    <row r="926" spans="3:3">
       <c r="C926" s="9"/>
     </row>
-    <row r="927">
-      <c r="A927" s="9"/>
-      <c r="B927" s="9"/>
+    <row r="927" spans="3:3">
       <c r="C927" s="9"/>
     </row>
-    <row r="928">
-      <c r="A928" s="9"/>
-      <c r="B928" s="9"/>
+    <row r="928" spans="3:3">
       <c r="C928" s="9"/>
     </row>
-    <row r="929">
-      <c r="A929" s="9"/>
-      <c r="B929" s="9"/>
+    <row r="929" spans="3:3">
       <c r="C929" s="9"/>
     </row>
-    <row r="930">
-      <c r="A930" s="9"/>
-      <c r="B930" s="9"/>
+    <row r="930" spans="3:3">
       <c r="C930" s="9"/>
     </row>
-    <row r="931">
-      <c r="A931" s="9"/>
-      <c r="B931" s="9"/>
+    <row r="931" spans="3:3">
       <c r="C931" s="9"/>
     </row>
-    <row r="932">
-      <c r="A932" s="9"/>
-      <c r="B932" s="9"/>
+    <row r="932" spans="3:3">
       <c r="C932" s="9"/>
     </row>
-    <row r="933">
-      <c r="A933" s="9"/>
-      <c r="B933" s="9"/>
+    <row r="933" spans="3:3">
       <c r="C933" s="9"/>
     </row>
-    <row r="934">
-      <c r="A934" s="9"/>
-      <c r="B934" s="9"/>
+    <row r="934" spans="3:3">
       <c r="C934" s="9"/>
     </row>
-    <row r="935">
-      <c r="A935" s="9"/>
-      <c r="B935" s="9"/>
+    <row r="935" spans="3:3">
       <c r="C935" s="9"/>
     </row>
-    <row r="936">
-      <c r="A936" s="9"/>
-      <c r="B936" s="9"/>
+    <row r="936" spans="3:3">
       <c r="C936" s="9"/>
     </row>
-    <row r="937">
-      <c r="A937" s="9"/>
-      <c r="B937" s="9"/>
+    <row r="937" spans="3:3">
       <c r="C937" s="9"/>
     </row>
-    <row r="938">
-      <c r="A938" s="9"/>
-      <c r="B938" s="9"/>
+    <row r="938" spans="3:3">
       <c r="C938" s="9"/>
     </row>
-    <row r="939">
-      <c r="A939" s="9"/>
-      <c r="B939" s="9"/>
+    <row r="939" spans="3:3">
       <c r="C939" s="9"/>
     </row>
-    <row r="940">
-      <c r="A940" s="9"/>
-      <c r="B940" s="9"/>
+    <row r="940" spans="3:3">
       <c r="C940" s="9"/>
     </row>
-    <row r="941">
-      <c r="A941" s="9"/>
-      <c r="B941" s="9"/>
+    <row r="941" spans="3:3">
       <c r="C941" s="9"/>
     </row>
-    <row r="942">
-      <c r="A942" s="9"/>
-      <c r="B942" s="9"/>
+    <row r="942" spans="3:3">
       <c r="C942" s="9"/>
     </row>
-    <row r="943">
-      <c r="A943" s="9"/>
-      <c r="B943" s="9"/>
+    <row r="943" spans="3:3">
       <c r="C943" s="9"/>
     </row>
-    <row r="944">
-      <c r="A944" s="9"/>
-      <c r="B944" s="9"/>
+    <row r="944" spans="3:3">
       <c r="C944" s="9"/>
     </row>
-    <row r="945">
-      <c r="A945" s="9"/>
-      <c r="B945" s="9"/>
+    <row r="945" spans="3:3">
       <c r="C945" s="9"/>
     </row>
-    <row r="946">
-      <c r="A946" s="9"/>
-      <c r="B946" s="9"/>
+    <row r="946" spans="3:3">
       <c r="C946" s="9"/>
     </row>
-    <row r="947">
-      <c r="A947" s="9"/>
-      <c r="B947" s="9"/>
+    <row r="947" spans="3:3">
       <c r="C947" s="9"/>
     </row>
-    <row r="948">
-      <c r="A948" s="9"/>
-      <c r="B948" s="9"/>
+    <row r="948" spans="3:3">
       <c r="C948" s="9"/>
     </row>
-    <row r="949">
-      <c r="A949" s="9"/>
-      <c r="B949" s="9"/>
+    <row r="949" spans="3:3">
       <c r="C949" s="9"/>
     </row>
-    <row r="950">
-      <c r="A950" s="9"/>
-      <c r="B950" s="9"/>
+    <row r="950" spans="3:3">
       <c r="C950" s="9"/>
     </row>
-    <row r="951">
-      <c r="A951" s="9"/>
-      <c r="B951" s="9"/>
+    <row r="951" spans="3:3">
       <c r="C951" s="9"/>
     </row>
-    <row r="952">
-      <c r="A952" s="9"/>
-      <c r="B952" s="9"/>
+    <row r="952" spans="3:3">
       <c r="C952" s="9"/>
     </row>
-    <row r="953">
-      <c r="A953" s="9"/>
-      <c r="B953" s="9"/>
+    <row r="953" spans="3:3">
       <c r="C953" s="9"/>
     </row>
-    <row r="954">
-      <c r="A954" s="9"/>
-      <c r="B954" s="9"/>
+    <row r="954" spans="3:3">
       <c r="C954" s="9"/>
     </row>
-    <row r="955">
-      <c r="A955" s="9"/>
-      <c r="B955" s="9"/>
+    <row r="955" spans="3:3">
       <c r="C955" s="9"/>
     </row>
-    <row r="956">
-      <c r="A956" s="9"/>
-      <c r="B956" s="9"/>
+    <row r="956" spans="3:3">
       <c r="C956" s="9"/>
     </row>
-    <row r="957">
-      <c r="A957" s="9"/>
-      <c r="B957" s="9"/>
+    <row r="957" spans="3:3">
       <c r="C957" s="9"/>
     </row>
-    <row r="958">
-      <c r="A958" s="9"/>
-      <c r="B958" s="9"/>
+    <row r="958" spans="3:3">
       <c r="C958" s="9"/>
     </row>
-    <row r="959">
-      <c r="A959" s="9"/>
-      <c r="B959" s="9"/>
+    <row r="959" spans="3:3">
       <c r="C959" s="9"/>
     </row>
-    <row r="960">
-      <c r="A960" s="9"/>
-      <c r="B960" s="9"/>
+    <row r="960" spans="3:3">
       <c r="C960" s="9"/>
     </row>
-    <row r="961">
-      <c r="A961" s="9"/>
-      <c r="B961" s="9"/>
+    <row r="961" spans="3:3">
       <c r="C961" s="9"/>
     </row>
-    <row r="962">
-      <c r="A962" s="9"/>
-      <c r="B962" s="9"/>
+    <row r="962" spans="3:3">
       <c r="C962" s="9"/>
     </row>
-    <row r="963">
-      <c r="A963" s="9"/>
-      <c r="B963" s="9"/>
+    <row r="963" spans="3:3">
       <c r="C963" s="9"/>
     </row>
-    <row r="964">
-      <c r="A964" s="9"/>
-      <c r="B964" s="9"/>
+    <row r="964" spans="3:3">
       <c r="C964" s="9"/>
     </row>
-    <row r="965">
-      <c r="A965" s="9"/>
-      <c r="B965" s="9"/>
+    <row r="965" spans="3:3">
       <c r="C965" s="9"/>
     </row>
-    <row r="966">
-      <c r="A966" s="9"/>
-      <c r="B966" s="9"/>
+    <row r="966" spans="3:3">
       <c r="C966" s="9"/>
     </row>
-    <row r="967">
-      <c r="A967" s="9"/>
-      <c r="B967" s="9"/>
+    <row r="967" spans="3:3">
       <c r="C967" s="9"/>
     </row>
-    <row r="968">
-      <c r="A968" s="9"/>
-      <c r="B968" s="9"/>
+    <row r="968" spans="3:3">
       <c r="C968" s="9"/>
     </row>
-    <row r="969">
-      <c r="A969" s="9"/>
-      <c r="B969" s="9"/>
+    <row r="969" spans="3:3">
       <c r="C969" s="9"/>
     </row>
-    <row r="970">
-      <c r="A970" s="9"/>
-      <c r="B970" s="9"/>
+    <row r="970" spans="3:3">
       <c r="C970" s="9"/>
     </row>
-    <row r="971">
-      <c r="A971" s="9"/>
-      <c r="B971" s="9"/>
+    <row r="971" spans="3:3">
       <c r="C971" s="9"/>
     </row>
-    <row r="972">
-      <c r="A972" s="9"/>
-      <c r="B972" s="9"/>
+    <row r="972" spans="3:3">
       <c r="C972" s="9"/>
     </row>
-    <row r="973">
-      <c r="A973" s="9"/>
-      <c r="B973" s="9"/>
+    <row r="973" spans="3:3">
       <c r="C973" s="9"/>
     </row>
-    <row r="974">
-      <c r="A974" s="9"/>
-      <c r="B974" s="9"/>
+    <row r="974" spans="3:3">
       <c r="C974" s="9"/>
     </row>
-    <row r="975">
-      <c r="A975" s="9"/>
-      <c r="B975" s="9"/>
+    <row r="975" spans="3:3">
       <c r="C975" s="9"/>
     </row>
-    <row r="976">
-      <c r="A976" s="9"/>
-      <c r="B976" s="9"/>
+    <row r="976" spans="3:3">
       <c r="C976" s="9"/>
     </row>
-    <row r="977">
-      <c r="A977" s="9"/>
-      <c r="B977" s="9"/>
+    <row r="977" spans="3:3">
       <c r="C977" s="9"/>
     </row>
-    <row r="978">
-      <c r="A978" s="9"/>
-      <c r="B978" s="9"/>
+    <row r="978" spans="3:3">
       <c r="C978" s="9"/>
     </row>
-    <row r="979">
-      <c r="A979" s="9"/>
-      <c r="B979" s="9"/>
+    <row r="979" spans="3:3">
       <c r="C979" s="9"/>
     </row>
-    <row r="980">
-      <c r="A980" s="9"/>
-      <c r="B980" s="9"/>
+    <row r="980" spans="3:3">
       <c r="C980" s="9"/>
     </row>
-    <row r="981">
-      <c r="A981" s="9"/>
-      <c r="B981" s="9"/>
+    <row r="981" spans="3:3">
       <c r="C981" s="9"/>
     </row>
-    <row r="982">
-      <c r="A982" s="9"/>
-      <c r="B982" s="9"/>
+    <row r="982" spans="3:3">
       <c r="C982" s="9"/>
     </row>
-    <row r="983">
-      <c r="A983" s="9"/>
-      <c r="B983" s="9"/>
+    <row r="983" spans="3:3">
       <c r="C983" s="9"/>
     </row>
-    <row r="984">
-      <c r="A984" s="9"/>
-      <c r="B984" s="9"/>
+    <row r="984" spans="3:3">
       <c r="C984" s="9"/>
     </row>
-    <row r="985">
-      <c r="A985" s="9"/>
-      <c r="B985" s="9"/>
+    <row r="985" spans="3:3">
       <c r="C985" s="9"/>
     </row>
-    <row r="986">
-      <c r="A986" s="9"/>
-      <c r="B986" s="9"/>
+    <row r="986" spans="3:3">
       <c r="C986" s="9"/>
     </row>
-    <row r="987">
-      <c r="A987" s="9"/>
-      <c r="B987" s="9"/>
+    <row r="987" spans="3:3">
       <c r="C987" s="9"/>
     </row>
-    <row r="988">
-      <c r="A988" s="9"/>
-      <c r="B988" s="9"/>
+    <row r="988" spans="3:3">
       <c r="C988" s="9"/>
     </row>
-    <row r="989">
-      <c r="A989" s="9"/>
-      <c r="B989" s="9"/>
+    <row r="989" spans="3:3">
       <c r="C989" s="9"/>
     </row>
-    <row r="990">
-      <c r="A990" s="9"/>
-      <c r="B990" s="9"/>
+    <row r="990" spans="3:3">
       <c r="C990" s="9"/>
     </row>
-    <row r="991">
-      <c r="A991" s="9"/>
-      <c r="B991" s="9"/>
+    <row r="991" spans="3:3">
       <c r="C991" s="9"/>
     </row>
-    <row r="992">
-      <c r="A992" s="9"/>
-      <c r="B992" s="9"/>
+    <row r="992" spans="3:3">
       <c r="C992" s="9"/>
     </row>
-    <row r="993">
-      <c r="A993" s="9"/>
-      <c r="B993" s="9"/>
+    <row r="993" spans="3:3">
       <c r="C993" s="9"/>
     </row>
-    <row r="994">
-      <c r="A994" s="9"/>
-      <c r="B994" s="9"/>
+    <row r="994" spans="3:3">
       <c r="C994" s="9"/>
     </row>
-    <row r="995">
-      <c r="A995" s="9"/>
-      <c r="B995" s="9"/>
+    <row r="995" spans="3:3">
       <c r="C995" s="9"/>
     </row>
-    <row r="996">
-      <c r="A996" s="9"/>
-      <c r="B996" s="9"/>
+    <row r="996" spans="3:3">
       <c r="C996" s="9"/>
     </row>
-    <row r="997">
-      <c r="A997" s="9"/>
-      <c r="B997" s="9"/>
+    <row r="997" spans="3:3">
       <c r="C997" s="9"/>
     </row>
-    <row r="998">
-      <c r="A998" s="9"/>
-      <c r="B998" s="9"/>
+    <row r="998" spans="3:3">
       <c r="C998" s="9"/>
     </row>
-    <row r="999">
-      <c r="A999" s="9"/>
-      <c r="B999" s="9"/>
+    <row r="999" spans="3:3">
       <c r="C999" s="9"/>
     </row>
-    <row r="1000">
-      <c r="A1000" s="9"/>
-      <c r="B1000" s="9"/>
+    <row r="1000" spans="3:3">
       <c r="C1000" s="9"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
 </worksheet>
 </file>